--- a/ETF_Worksheet.xlsx
+++ b/ETF_Worksheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\EMP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\infomax\Documents\market_db_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57536474-A4C6-4911-8C7F-83217BEEF3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0829A20B-1221-4D3F-A0C3-079B1EAD9F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{0DAB313A-31E0-4EC0-BA56-6173326343FD}"/>
+    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="16440" xr2:uid="{0DAB313A-31E0-4EC0-BA56-6173326343FD}"/>
   </bookViews>
   <sheets>
     <sheet name="PDF정보" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{2DB8C218-6486-4807-B223-0939FB9D934A}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{2DB8C218-6486-4807-B223-0939FB9D934A}">
       <text>
         <r>
           <rPr>
@@ -72,7 +72,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{0736DB3A-61D9-4437-83C7-5BE0DC4980B3}">
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{0736DB3A-61D9-4437-83C7-5BE0DC4980B3}">
       <text>
         <r>
           <rPr>
@@ -86,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{4C39715C-124D-429A-B469-F18937CE246F}">
+    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{4C39715C-124D-429A-B469-F18937CE246F}">
       <text>
         <r>
           <rPr>
@@ -100,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0" shapeId="0" xr:uid="{0AB808D7-BC41-4A74-B388-3A67588FABC9}">
+    <comment ref="AA3" authorId="0" shapeId="0" xr:uid="{0AB808D7-BC41-4A74-B388-3A67588FABC9}">
       <text>
         <r>
           <rPr>
@@ -114,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="0" shapeId="0" xr:uid="{5D2B3F5C-5DF2-465B-98ED-2284CF6B29D9}">
+    <comment ref="AG3" authorId="0" shapeId="0" xr:uid="{5D2B3F5C-5DF2-465B-98ED-2284CF6B29D9}">
       <text>
         <r>
           <rPr>
@@ -128,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG3" authorId="0" shapeId="0" xr:uid="{3F0FD9C9-EDEA-4010-992E-E89413E00C57}">
+    <comment ref="AM3" authorId="0" shapeId="0" xr:uid="{3F0FD9C9-EDEA-4010-992E-E89413E00C57}">
       <text>
         <r>
           <rPr>
@@ -142,7 +142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL3" authorId="0" shapeId="0" xr:uid="{AAE95A8D-21CD-456F-B5C2-9CBD67B421FF}">
+    <comment ref="AS3" authorId="0" shapeId="0" xr:uid="{AAE95A8D-21CD-456F-B5C2-9CBD67B421FF}">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ3" authorId="0" shapeId="0" xr:uid="{2483CD64-D375-42B3-87DD-C97D23DF021A}">
+    <comment ref="AY3" authorId="0" shapeId="0" xr:uid="{2483CD64-D375-42B3-87DD-C97D23DF021A}">
       <text>
         <r>
           <rPr>
@@ -170,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AV3" authorId="0" shapeId="0" xr:uid="{57544528-E15A-43A9-825C-70102E7419BE}">
+    <comment ref="BE3" authorId="0" shapeId="0" xr:uid="{57544528-E15A-43A9-825C-70102E7419BE}">
       <text>
         <r>
           <rPr>
@@ -184,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BA3" authorId="0" shapeId="0" xr:uid="{6C6267A8-513B-40DF-AD0B-34452353A6B2}">
+    <comment ref="BK3" authorId="0" shapeId="0" xr:uid="{6C6267A8-513B-40DF-AD0B-34452353A6B2}">
       <text>
         <r>
           <rPr>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="1406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="1408">
   <si>
     <t>코드</t>
   </si>
@@ -4421,6 +4421,13 @@
   </si>
   <si>
     <t>ETF괴리율</t>
+  </si>
+  <si>
+    <t>상장주식수</t>
+  </si>
+  <si>
+    <t>상장주식수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4661,200 +4668,200 @@
       <tp>
         <v>0</v>
         <stp/>
-        <stp>H</stp>
-        <stp>x20.md171_0</stp>
-        <stp>159</stp>
-        <stp>993374</stp>
-        <tr r="AJ2" s="2"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
         <stp>T</stp>
-        <stp>x10.md171_0</stp>
-        <stp>149</stp>
-        <stp>993374</stp>
+        <stp>x7.ww171_0</stp>
+        <stp>166</stp>
+        <stp>1711024</stp>
         <tr r="AO7" s="1"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
+        <stp>T</stp>
+        <stp>x2.ww171_0</stp>
+        <stp>161</stp>
+        <stp>1711024</stp>
+        <tr r="BI7" s="1"/>
+      </tp>
+      <tp>
+        <v>0</v>
+        <stp/>
+        <stp>T</stp>
+        <stp>x6.ww171_0</stp>
+        <stp>165</stp>
+        <stp>1711024</stp>
+        <tr r="AY7" s="1"/>
+      </tp>
+      <tp>
+        <v>0</v>
+        <stp/>
+        <stp>T</stp>
+        <stp>x4.ww171_0</stp>
+        <stp>163</stp>
+        <stp>1711024</stp>
+        <tr r="A7" s="1"/>
+      </tp>
+      <tp>
+        <v>0</v>
+        <stp/>
         <stp>H</stp>
-        <stp>x12.md171_0</stp>
-        <stp>151</stp>
-        <stp>993374</stp>
+        <stp>x8.ww171_0</stp>
+        <stp>187</stp>
+        <stp>1711024</stp>
+        <tr r="BI2" s="2"/>
+      </tp>
+      <tp>
+        <v>0</v>
+        <stp/>
+        <stp>H</stp>
+        <stp>x9.ww171_0</stp>
+        <stp>189</stp>
+        <stp>1711024</stp>
+        <tr r="AK2" s="2"/>
+      </tp>
+      <tp t="e">
+        <v>#N/A</v>
+        <stp/>
+        <stp>H</stp>
+        <stp>x3.ww171_0</stp>
+        <stp>193</stp>
+        <stp>1711024</stp>
+        <tr r="S2" s="2"/>
+      </tp>
+      <tp t="e">
+        <v>#N/A</v>
+        <stp/>
+        <stp>H</stp>
+        <stp>x1.ww171_0</stp>
+        <stp>194</stp>
+        <stp>1711024</stp>
+        <tr r="Y2" s="2"/>
+      </tp>
+      <tp t="e">
+        <v>#N/A</v>
+        <stp/>
+        <stp>H</stp>
+        <stp>x5.ww171_0</stp>
+        <stp>191</stp>
+        <stp>1711024</stp>
+        <tr r="G2" s="2"/>
+      </tp>
+      <tp>
+        <v>0</v>
+        <stp/>
+        <stp>H</stp>
+        <stp>x1.xw171_0</stp>
+        <stp>188</stp>
+        <stp>1711024</stp>
+        <tr r="AQ2" s="2"/>
+      </tp>
+      <tp>
+        <v>0</v>
+        <stp/>
+        <stp>T</stp>
+        <stp>x3.xw171_0</stp>
+        <stp>181</stp>
+        <stp>1711024</stp>
+        <tr r="CW7" s="1"/>
+      </tp>
+      <tp t="e">
+        <v>#N/A</v>
+        <stp/>
+        <stp>H</stp>
+        <stp>x2.xw171_0</stp>
+        <stp>195</stp>
+        <stp>1711024</stp>
         <tr r="AE2" s="2"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
-        <stp>H</stp>
-        <stp>x16.md171_0</stp>
-        <stp>155</stp>
-        <stp>993374</stp>
-        <tr r="A2" s="2"/>
+        <stp>T</stp>
+        <stp>x11.ww171_0</stp>
+        <stp>170</stp>
+        <stp>1711024</stp>
+        <tr r="AE7" s="1"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
-        <stp>H</stp>
-        <stp>x11.md171_0</stp>
-        <stp>150</stp>
-        <stp>993374</stp>
-        <tr r="AY2" s="2"/>
+        <stp>T</stp>
+        <stp>x13.ww171_0</stp>
+        <stp>172</stp>
+        <stp>1711024</stp>
+        <tr r="CM7" s="1"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
-        <stp>H</stp>
-        <stp>x19.md171_0</stp>
-        <stp>158</stp>
-        <stp>993374</stp>
-        <tr r="AO2" s="2"/>
+        <stp>T</stp>
+        <stp>x15.ww171_0</stp>
+        <stp>174</stp>
+        <stp>1711024</stp>
+        <tr r="CC7" s="1"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
-        <stp>H</stp>
-        <stp>x18.md171_0</stp>
-        <stp>157</stp>
-        <stp>993374</stp>
-        <tr r="AT2" s="2"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
         <stp>T</stp>
-        <stp>x14.md171_0</stp>
-        <stp>153</stp>
-        <stp>993374</stp>
+        <stp>x12.ww171_0</stp>
+        <stp>171</stp>
+        <stp>1711024</stp>
         <tr r="K7" s="1"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
         <stp>T</stp>
-        <stp>x13.md171_0</stp>
-        <stp>152</stp>
-        <stp>993374</stp>
-        <tr r="AE7" s="1"/>
+        <stp>x16.ww171_0</stp>
+        <stp>175</stp>
+        <stp>1711024</stp>
+        <tr r="BS7" s="1"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
         <stp>T</stp>
-        <stp>x15.md171_0</stp>
-        <stp>154</stp>
-        <stp>993374</stp>
+        <stp>x14.ww171_0</stp>
+        <stp>173</stp>
+        <stp>1711024</stp>
         <tr r="U7" s="1"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
-        <stp>T</stp>
-        <stp>x17.md171_0</stp>
-        <stp>156</stp>
-        <stp>993374</stp>
-        <tr r="A7" s="1"/>
+        <stp>H</stp>
+        <stp>x10.ww171_0</stp>
+        <stp>190</stp>
+        <stp>1711024</stp>
+        <tr r="A2" s="2"/>
+      </tp>
+      <tp t="e">
+        <v>#N/A</v>
+        <stp/>
+        <stp>H</stp>
+        <stp>x18.ww171_0</stp>
+        <stp>192</stp>
+        <stp>1711024</stp>
+        <tr r="M2" s="2"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
-        <stp>T</stp>
-        <stp>x4.md171_0</stp>
-        <stp>143</stp>
-        <stp>993374</stp>
-        <tr r="BS7" s="1"/>
+        <stp>H</stp>
+        <stp>x17.ww171_0</stp>
+        <stp>186</stp>
+        <stp>1711024</stp>
+        <tr r="BC2" s="2"/>
       </tp>
       <tp>
         <v>0</v>
         <stp/>
-        <stp>T</stp>
-        <stp>x2.md171_0</stp>
-        <stp>141</stp>
-        <stp>993374</stp>
-        <tr r="CM7" s="1"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
-        <stp>T</stp>
-        <stp>x6.md171_0</stp>
-        <stp>145</stp>
-        <stp>993374</stp>
-        <tr r="AY7" s="1"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
-        <stp>T</stp>
-        <stp>x1.md171_0</stp>
-        <stp>140</stp>
-        <stp>993374</stp>
-        <tr r="CW7" s="1"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
-        <stp>T</stp>
-        <stp>x3.md171_0</stp>
-        <stp>142</stp>
-        <stp>993374</stp>
-        <tr r="CC7" s="1"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
-        <stp>T</stp>
-        <stp>x5.md171_0</stp>
-        <stp>144</stp>
-        <stp>993374</stp>
-        <tr r="BI7" s="1"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
         <stp>H</stp>
-        <stp>x2.ld171_0</stp>
-        <stp>139</stp>
-        <stp>993374</stp>
-        <tr r="F2" s="2"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
-        <stp>H</stp>
-        <stp>x1.ld171_0</stp>
-        <stp>138</stp>
-        <stp>993374</stp>
-        <tr r="K2" s="2"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
-        <stp>H</stp>
-        <stp>x8.md171_0</stp>
-        <stp>147</stp>
-        <stp>993374</stp>
-        <tr r="U2" s="2"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
-        <stp>H</stp>
-        <stp>x7.md171_0</stp>
-        <stp>146</stp>
-        <stp>993374</stp>
-        <tr r="Z2" s="2"/>
-      </tp>
-      <tp>
-        <v>0</v>
-        <stp/>
-        <stp>H</stp>
-        <stp>x9.md171_0</stp>
-        <stp>148</stp>
-        <stp>993374</stp>
-        <tr r="P2" s="2"/>
+        <stp>x19.ww171_0</stp>
+        <stp>184</stp>
+        <stp>1711024</stp>
+        <tr r="AW2" s="2"/>
       </tp>
     </main>
   </volType>
@@ -29985,7 +29992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57D12DD-08A7-4C8E-ACAC-FF311AD3CE0A}">
-  <dimension ref="A1:BC33"/>
+  <dimension ref="A1:BN33"/>
   <sheetFormatPr defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.75" bestFit="1" customWidth="1"/>
@@ -30000,45 +30007,52 @@
     <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.125" customWidth="1"/>
+    <col min="17" max="17" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.125" customWidth="1"/>
+    <col min="23" max="23" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.125" customWidth="1"/>
+    <col min="29" max="29" width="9.75" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.125" customWidth="1"/>
+    <col min="35" max="35" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.125" customWidth="1"/>
     <col min="41" max="41" width="9.75" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="9.125" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.125" customWidth="1"/>
+    <col min="47" max="47" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="9.125" customWidth="1"/>
+    <col min="54" max="54" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="56" max="57" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="9.125" customWidth="1"/>
+    <col min="60" max="60" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1394</v>
       </c>
@@ -30109,7 +30123,6 @@
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
-      <c r="AQ1" s="3"/>
       <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3"/>
@@ -30122,98 +30135,106 @@
       <c r="BA1" s="3"/>
       <c r="BB1" s="3"/>
       <c r="BC1" s="3"/>
+      <c r="BD1" s="3"/>
+      <c r="BE1" s="3"/>
+      <c r="BF1" s="3"/>
+      <c r="BG1" s="3"/>
+      <c r="BH1" s="3"/>
+      <c r="BI1" s="3"/>
+      <c r="BJ1" s="3"/>
+      <c r="BK1" s="3"/>
+      <c r="BL1" s="3"/>
     </row>
-    <row r="2" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="str">
-        <f>_xll.IMDH("STK","273130",A3:E3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=KODEX 종합채권(AA-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+        <f>_xll.IMDH("STK","273130",A3:F3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=KODEX 종합채권(AA-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
         <v>KODEX 종합채권(AA-이상)액티브</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3" t="str">
-        <f>_xll.IMDH("STK","363570",F3:J3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=KODEX 장기종합채권(AA-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+      <c r="G2" s="3" t="str">
+        <f>_xll.IMDH("STK","363570",G3:L3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=KODEX 장기종합채권(AA-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
         <v>KODEX 장기종합채권(AA-이상)액티브</v>
       </c>
-      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3" t="str">
-        <f>_xll.IMDH("STK","439870",K3:O3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=KODEX 국고채30년액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="str">
+        <f>_xll.IMDH("STK","439870",M3:R3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=KODEX 국고채30년액티브,DtFmt=1,TmFmt=1,unit=true")</f>
         <v>KODEX 국고채30년액티브</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="3" t="str">
-        <f>_xll.IMDH("STK","438570",P3:T3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 국고채10년,DtFmt=1,TmFmt=1,unit=true")</f>
+      <c r="P2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3" t="str">
+        <f>_xll.IMDH("STK","438570",S3:X3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 국고채10년,DtFmt=1,TmFmt=1,unit=true")</f>
         <v>SOL 국고채10년</v>
       </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="3" t="str">
-        <f>_xll.IMDH("STK","438560",U3:Y3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 국고채3년,DtFmt=1,TmFmt=1,unit=true")</f>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3" t="str">
+        <f>_xll.IMDH("STK","438560",Y3:AD3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 국고채3년,DtFmt=1,TmFmt=1,unit=true")</f>
         <v>SOL 국고채3년</v>
       </c>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3" t="str">
-        <f>_xll.IMDH("STK","436140",Z3:AD3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 종합채권(AA-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
-        <v>SOL 종합채권(AA-이상)액티브</v>
-      </c>
+      <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
       <c r="AE2" s="3" t="str">
-        <f>_xll.IMDH("STK","469830",AE3:AI3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 초단기채권액티브,DtFmt=1,TmFmt=1,unit=true")</f>
-        <v>SOL 초단기채권액티브</v>
+        <f>_xll.IMDH("STK","436140",AE3:AJ3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 종합채권(AA-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+        <v>SOL 종합채권(AA-이상)액티브</v>
       </c>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3" t="str">
-        <f>_xll.IMDH("STK","0016X0",AJ3:AN3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 중단기회사채(A-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
-        <v>SOL 중단기회사채(A-이상)액티브</v>
-      </c>
-      <c r="AK2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3" t="str">
+        <f>_xll.IMDH("STK","469830",AK3:AP3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 초단기채권액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+        <v>SOL 초단기채권액티브</v>
+      </c>
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
-      <c r="AO2" s="3" t="str">
-        <f>_xll.IMDH("STK","385540",AO3:AS3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=RISE 종합채권(A-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
-        <v>RISE 종합채권(A-이상)액티브</v>
-      </c>
       <c r="AP2" s="3"/>
-      <c r="AQ2" s="3"/>
+      <c r="AQ2" s="3" t="str">
+        <f>_xll.IMDH("STK","0016X0",AQ3:AV3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 중단기회사채(A-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+        <v>SOL 중단기회사채(A-이상)액티브</v>
+      </c>
       <c r="AR2" s="3"/>
       <c r="AS2" s="3"/>
-      <c r="AT2" s="3" t="str">
-        <f>_xll.IMDH("STK","0141T0",AT3:AX3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 중기종합채권(AA-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
-        <v>SOL 중기종합채권(AA-이상)액티브</v>
-      </c>
-      <c r="AU2" s="3"/>
+      <c r="AT2" s="3"/>
       <c r="AV2" s="3"/>
-      <c r="AW2" s="3"/>
+      <c r="AW2" s="3" t="str">
+        <f>_xll.IMDH("STK","385540",AW3:BB3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=RISE 종합채권(A-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+        <v>RISE 종합채권(A-이상)액티브</v>
+      </c>
       <c r="AX2" s="3"/>
-      <c r="AY2" s="3" t="str">
-        <f>_xll.IMDH("STK","438330",AY3:BC3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=TIGER 우량회사채액티브,DtFmt=1,TmFmt=1,unit=true")</f>
-        <v>TIGER 우량회사채액티브</v>
-      </c>
+      <c r="AY2" s="3"/>
       <c r="AZ2" s="3"/>
       <c r="BA2" s="3"/>
-      <c r="BB2" s="3"/>
-      <c r="BC2" s="3"/>
+      <c r="BC2" s="3" t="str">
+        <f>_xll.IMDH("STK","0141T0",BC3:BH3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=SOL 중기종합채권(AA-이상)액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+        <v>SOL 중기종합채권(AA-이상)액티브</v>
+      </c>
+      <c r="BD2" s="3"/>
+      <c r="BE2" s="3"/>
+      <c r="BF2" s="3"/>
+      <c r="BG2" s="3"/>
+      <c r="BI2" s="3" t="str">
+        <f>_xll.IMDH("STK","438330",BI3:BN3,$B$1,$D$1,$F$1,"Per="&amp;$H$1&amp;",sort="&amp;$J$1&amp;",real=false,Bizday="&amp;$L$1&amp;",Quote="&amp;$N$1&amp;",Pos=20,Orient=V,Title=TIGER 우량회사채액티브,DtFmt=1,TmFmt=1,unit=true")</f>
+        <v>TIGER 우량회사채액티브</v>
+      </c>
+      <c r="BJ2" s="3"/>
+      <c r="BK2" s="3"/>
+      <c r="BL2" s="3"/>
     </row>
-    <row r="3" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -30229,158 +30250,191 @@
       <c r="E3" s="5" t="s">
         <v>1405</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>1402</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>1403</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>1404</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>1405</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="6" t="s">
+        <v>1406</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>1402</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>1403</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>1404</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>1405</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="R3" s="7" t="s">
+        <v>1406</v>
+      </c>
+      <c r="S3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="T3" s="8" t="s">
         <v>1402</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="U3" s="8" t="s">
         <v>1403</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="V3" s="8" t="s">
         <v>1404</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="W3" s="8" t="s">
         <v>1405</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="X3" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="Y3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>1402</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>1403</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="AB3" s="9" t="s">
         <v>1404</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="AC3" s="9" t="s">
         <v>1405</v>
       </c>
-      <c r="Z3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="10" t="s">
-        <v>1402</v>
-      </c>
-      <c r="AB3" s="10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="AC3" s="10" t="s">
-        <v>1404</v>
-      </c>
-      <c r="AD3" s="10" t="s">
-        <v>1405</v>
+      <c r="AD3" s="9" t="s">
+        <v>1406</v>
       </c>
       <c r="AE3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AF3" s="11" t="s">
+      <c r="AF3" s="10" t="s">
         <v>1402</v>
       </c>
-      <c r="AG3" s="11" t="s">
+      <c r="AG3" s="10" t="s">
         <v>1403</v>
       </c>
-      <c r="AH3" s="11" t="s">
+      <c r="AH3" s="10" t="s">
         <v>1404</v>
       </c>
-      <c r="AI3" s="11" t="s">
+      <c r="AI3" s="10" t="s">
         <v>1405</v>
       </c>
-      <c r="AJ3" s="4" t="s">
+      <c r="AJ3" s="10" t="s">
+        <v>1406</v>
+      </c>
+      <c r="AK3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AK3" s="12" t="s">
+      <c r="AL3" s="11" t="s">
         <v>1402</v>
       </c>
-      <c r="AL3" s="12" t="s">
+      <c r="AM3" s="11" t="s">
         <v>1403</v>
       </c>
-      <c r="AM3" s="12" t="s">
+      <c r="AN3" s="11" t="s">
         <v>1404</v>
       </c>
-      <c r="AN3" s="12" t="s">
+      <c r="AO3" s="11" t="s">
         <v>1405</v>
       </c>
-      <c r="AO3" s="4" t="s">
+      <c r="AP3" s="11" t="s">
+        <v>1406</v>
+      </c>
+      <c r="AQ3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AP3" s="13" t="s">
+      <c r="AR3" s="12" t="s">
         <v>1402</v>
       </c>
-      <c r="AQ3" s="13" t="s">
+      <c r="AS3" s="12" t="s">
         <v>1403</v>
       </c>
-      <c r="AR3" s="13" t="s">
+      <c r="AT3" s="12" t="s">
         <v>1404</v>
       </c>
-      <c r="AS3" s="13" t="s">
+      <c r="AU3" s="12" t="s">
         <v>1405</v>
       </c>
-      <c r="AT3" s="4" t="s">
+      <c r="AV3" s="12" t="s">
+        <v>1406</v>
+      </c>
+      <c r="AW3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AU3" s="14" t="s">
+      <c r="AX3" s="13" t="s">
         <v>1402</v>
       </c>
-      <c r="AV3" s="14" t="s">
+      <c r="AY3" s="13" t="s">
         <v>1403</v>
       </c>
-      <c r="AW3" s="14" t="s">
+      <c r="AZ3" s="13" t="s">
         <v>1404</v>
       </c>
-      <c r="AX3" s="14" t="s">
+      <c r="BA3" s="13" t="s">
         <v>1405</v>
       </c>
-      <c r="AY3" s="4" t="s">
+      <c r="BB3" s="13" t="s">
+        <v>1407</v>
+      </c>
+      <c r="BC3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AZ3" s="15" t="s">
+      <c r="BD3" s="14" t="s">
         <v>1402</v>
       </c>
-      <c r="BA3" s="15" t="s">
+      <c r="BE3" s="14" t="s">
         <v>1403</v>
       </c>
-      <c r="BB3" s="15" t="s">
+      <c r="BF3" s="14" t="s">
         <v>1404</v>
       </c>
-      <c r="BC3" s="15" t="s">
+      <c r="BG3" s="14" t="s">
         <v>1405</v>
       </c>
+      <c r="BH3" s="14" t="s">
+        <v>1406</v>
+      </c>
+      <c r="BI3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="BJ3" s="15" t="s">
+        <v>1402</v>
+      </c>
+      <c r="BK3" s="15" t="s">
+        <v>1403</v>
+      </c>
+      <c r="BL3" s="15" t="s">
+        <v>1404</v>
+      </c>
+      <c r="BM3" s="15" t="s">
+        <v>1405</v>
+      </c>
+      <c r="BN3" s="15" t="s">
+        <v>1406</v>
+      </c>
     </row>
-    <row r="4" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46197</v>
       </c>
@@ -30391,163 +30445,196 @@
         <v>4182666989904</v>
       </c>
       <c r="D4" s="3">
-        <v>110206.74</v>
+        <v>110218.82</v>
       </c>
       <c r="E4" s="3">
-        <v>-8.3243999999999999E-2</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46197</v>
-      </c>
-      <c r="G4" s="3">
+        <v>-0.18945899999999999</v>
+      </c>
+      <c r="F4" s="3">
+        <v>37915000</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="H4" s="3">
         <v>87580</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>281732680237</v>
       </c>
-      <c r="I4" s="3">
-        <v>87565.26</v>
-      </c>
       <c r="J4" s="3">
-        <v>-6.8817000000000003E-2</v>
-      </c>
-      <c r="K4" s="2">
-        <v>46197</v>
+        <v>87586.44</v>
+      </c>
+      <c r="K4" s="3">
+        <v>-0.115817</v>
       </c>
       <c r="L4" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="M4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="N4" s="3">
         <v>90830</v>
       </c>
-      <c r="M4" s="3">
+      <c r="O4" s="3">
         <v>389302349880</v>
       </c>
-      <c r="N4" s="3">
-        <v>90590.69</v>
-      </c>
-      <c r="O4" s="3">
-        <v>-0.29328599999999999</v>
-      </c>
-      <c r="P4" s="2">
-        <v>46197</v>
+      <c r="P4" s="3">
+        <v>90690.12</v>
       </c>
       <c r="Q4" s="3">
+        <v>-0.61210600000000004</v>
+      </c>
+      <c r="R4" s="3">
+        <v>4271000</v>
+      </c>
+      <c r="S4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="T4" s="3">
         <v>98600</v>
       </c>
-      <c r="R4" s="3">
+      <c r="U4" s="3">
         <v>106449228327</v>
       </c>
-      <c r="S4" s="3">
-        <v>98538.84</v>
-      </c>
-      <c r="T4" s="3">
-        <v>6.2066999999999997E-2</v>
-      </c>
-      <c r="U4" s="2">
-        <v>46197</v>
-      </c>
       <c r="V4" s="3">
+        <v>98560.07</v>
+      </c>
+      <c r="W4" s="3">
+        <v>-9.1385999999999995E-2</v>
+      </c>
+      <c r="X4" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="Z4" s="3">
         <v>99970</v>
       </c>
-      <c r="W4" s="3">
+      <c r="AA4" s="3">
         <v>73765876251</v>
       </c>
-      <c r="X4" s="3">
-        <v>99906.6</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>1.8416999999999999E-2</v>
-      </c>
-      <c r="Z4" s="2">
-        <v>46197</v>
-      </c>
-      <c r="AA4" s="3">
+      <c r="AB4" s="3">
+        <v>99899.33</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>6.7100000000000005E-4</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>738000</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="AF4" s="3">
         <v>106330</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AG4" s="3">
         <v>1380634080717</v>
       </c>
-      <c r="AC4" s="3">
-        <v>106461.85</v>
-      </c>
-      <c r="AD4" s="3">
-        <v>-0.123847</v>
-      </c>
-      <c r="AE4" s="2">
-        <v>46197</v>
-      </c>
-      <c r="AF4" s="3">
+      <c r="AH4" s="3">
+        <v>106475.45</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>-0.136604</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>12952000</v>
+      </c>
+      <c r="AK4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="AL4" s="3">
         <v>54010</v>
       </c>
-      <c r="AG4" s="3">
+      <c r="AM4" s="3">
         <v>1167653722674</v>
       </c>
-      <c r="AH4" s="3">
+      <c r="AN4" s="3">
         <v>54014.47</v>
       </c>
-      <c r="AI4" s="3">
-        <v>-4.5729999999999998E-3</v>
-      </c>
-      <c r="AJ4" s="2">
-        <v>46197</v>
-      </c>
-      <c r="AK4" s="3">
+      <c r="AO4" s="3">
+        <v>-8.2760000000000004E-3</v>
+      </c>
+      <c r="AP4" s="3">
+        <v>21622000</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="AR4" s="3">
         <v>51075</v>
       </c>
-      <c r="AL4" s="3">
+      <c r="AS4" s="3">
         <v>405381562400</v>
       </c>
-      <c r="AM4" s="3">
-        <v>51071.62</v>
-      </c>
-      <c r="AN4" s="3">
-        <v>-2.2752000000000001E-2</v>
-      </c>
-      <c r="AO4" s="2">
-        <v>46197</v>
-      </c>
-      <c r="AP4" s="3">
+      <c r="AT4" s="3">
+        <v>51066.37</v>
+      </c>
+      <c r="AU4" s="3">
+        <v>-1.2474000000000001E-2</v>
+      </c>
+      <c r="AV4" s="3">
+        <v>7938000</v>
+      </c>
+      <c r="AW4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="AX4" s="3">
         <v>103230</v>
       </c>
-      <c r="AQ4" s="3">
+      <c r="AY4" s="3">
         <v>2205422646363</v>
       </c>
-      <c r="AR4" s="3">
-        <v>103152.18</v>
-      </c>
-      <c r="AS4" s="3">
-        <v>-3.6044E-2</v>
-      </c>
-      <c r="AT4" s="2">
-        <v>46197</v>
-      </c>
-      <c r="AU4" s="3">
+      <c r="AZ4" s="3">
+        <v>103037.08</v>
+      </c>
+      <c r="BA4" s="3">
+        <v>-5.0545E-2</v>
+      </c>
+      <c r="BB4" s="3">
+        <v>21352000</v>
+      </c>
+      <c r="BC4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="BD4" s="3">
         <v>49975</v>
       </c>
-      <c r="AV4" s="3">
+      <c r="BE4" s="3">
         <v>36909571802</v>
       </c>
-      <c r="AW4" s="3">
-        <v>50003.48</v>
-      </c>
-      <c r="AX4" s="3">
-        <v>-5.6956E-2</v>
-      </c>
-      <c r="AY4" s="2">
-        <v>46197</v>
-      </c>
-      <c r="AZ4" s="3">
+      <c r="BF4" s="3">
+        <v>50002.57</v>
+      </c>
+      <c r="BG4" s="3">
+        <v>-5.5136999999999999E-2</v>
+      </c>
+      <c r="BH4" s="3">
+        <v>738000</v>
+      </c>
+      <c r="BI4" s="2">
+        <v>46197</v>
+      </c>
+      <c r="BJ4" s="3">
         <v>114705</v>
       </c>
-      <c r="BA4" s="3">
+      <c r="BK4" s="3">
         <v>553258330974</v>
       </c>
-      <c r="BB4" s="3">
-        <v>114797.77</v>
-      </c>
-      <c r="BC4" s="3">
-        <v>-0.1113</v>
+      <c r="BL4" s="3">
+        <v>114793.31</v>
+      </c>
+      <c r="BM4" s="3">
+        <v>-0.11613</v>
+      </c>
+      <c r="BN4" s="3">
+        <v>4821000</v>
       </c>
     </row>
-    <row r="5" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>46196</v>
       </c>
@@ -30563,158 +30650,191 @@
       <c r="E5" s="3">
         <v>-0.06</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
+        <v>37356000</v>
+      </c>
+      <c r="G5" s="2">
         <v>46196</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>87650</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>281438357882</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>87821.91</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="M5" s="2">
         <v>46196</v>
       </c>
-      <c r="L5" s="3">
+      <c r="N5" s="3">
         <v>91180</v>
       </c>
-      <c r="M5" s="3">
+      <c r="O5" s="3">
         <v>389453634025</v>
       </c>
-      <c r="N5" s="3">
+      <c r="P5" s="3">
         <v>91150.16</v>
       </c>
-      <c r="O5" s="3">
+      <c r="Q5" s="3">
         <v>-0.35</v>
       </c>
-      <c r="P5" s="2">
+      <c r="R5" s="3">
+        <v>4272000</v>
+      </c>
+      <c r="S5" s="2">
         <v>46196</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="T5" s="3">
         <v>98380</v>
       </c>
-      <c r="R5" s="3">
+      <c r="U5" s="3">
         <v>106166835847</v>
       </c>
-      <c r="S5" s="3">
+      <c r="V5" s="3">
         <v>98746.97</v>
       </c>
-      <c r="T5" s="3">
+      <c r="W5" s="3">
         <v>-0.15</v>
       </c>
-      <c r="U5" s="2">
+      <c r="X5" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="Y5" s="2">
         <v>46196</v>
       </c>
-      <c r="V5" s="3">
+      <c r="Z5" s="3">
         <v>99775</v>
       </c>
-      <c r="W5" s="3">
+      <c r="AA5" s="3">
         <v>73667694472</v>
       </c>
-      <c r="X5" s="3">
+      <c r="AB5" s="3">
         <v>99953.76</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="AC5" s="3">
         <v>0.02</v>
       </c>
-      <c r="Z5" s="2">
-        <v>46196</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>106460</v>
-      </c>
-      <c r="AB5" s="3">
-        <v>1357128855658</v>
-      </c>
-      <c r="AC5" s="3">
-        <v>106596.21</v>
-      </c>
       <c r="AD5" s="3">
-        <v>-0.25</v>
+        <v>738000</v>
       </c>
       <c r="AE5" s="2">
         <v>46196</v>
       </c>
       <c r="AF5" s="3">
+        <v>106460</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>1357128855658</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>106596.21</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="AJ5" s="3">
+        <v>12743000</v>
+      </c>
+      <c r="AK5" s="2">
+        <v>46196</v>
+      </c>
+      <c r="AL5" s="3">
         <v>54010</v>
       </c>
-      <c r="AG5" s="3">
+      <c r="AM5" s="3">
         <v>1164324165373</v>
       </c>
-      <c r="AH5" s="3">
+      <c r="AN5" s="3">
         <v>54003.040000000001</v>
       </c>
-      <c r="AI5" s="3">
+      <c r="AO5" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ5" s="2">
+      <c r="AP5" s="3">
+        <v>21562000</v>
+      </c>
+      <c r="AQ5" s="2">
         <v>46196</v>
       </c>
-      <c r="AK5" s="3">
+      <c r="AR5" s="3">
         <v>51060</v>
       </c>
-      <c r="AL5" s="3">
+      <c r="AS5" s="3">
         <v>405253690956</v>
       </c>
-      <c r="AM5" s="3">
+      <c r="AT5" s="3">
         <v>51068.480000000003</v>
       </c>
-      <c r="AN5" s="3">
+      <c r="AU5" s="3">
         <v>0.01</v>
       </c>
-      <c r="AO5" s="2">
+      <c r="AV5" s="3">
+        <v>7938000</v>
+      </c>
+      <c r="AW5" s="2">
         <v>46196</v>
       </c>
-      <c r="AP5" s="3">
+      <c r="AX5" s="3">
         <v>103165</v>
       </c>
-      <c r="AQ5" s="3">
+      <c r="AY5" s="3">
         <v>2182859800821</v>
       </c>
-      <c r="AR5" s="3">
+      <c r="AZ5" s="3">
         <v>103288.81</v>
       </c>
-      <c r="AS5" s="3">
+      <c r="BA5" s="3">
         <v>-0.06</v>
       </c>
-      <c r="AT5" s="2">
+      <c r="BB5" s="3">
+        <v>21151000</v>
+      </c>
+      <c r="BC5" s="2">
         <v>46196</v>
       </c>
-      <c r="AU5" s="3">
+      <c r="BD5" s="3">
         <v>49945</v>
       </c>
-      <c r="AV5" s="3">
+      <c r="BE5" s="3">
         <v>36872644593</v>
       </c>
-      <c r="AW5" s="3">
+      <c r="BF5" s="3">
         <v>50012.97</v>
       </c>
-      <c r="AX5" s="3">
+      <c r="BG5" s="3">
         <v>-0.08</v>
       </c>
-      <c r="AY5" s="2">
+      <c r="BH5" s="3">
+        <v>738000</v>
+      </c>
+      <c r="BI5" s="2">
         <v>46196</v>
       </c>
-      <c r="AZ5" s="3">
+      <c r="BJ5" s="3">
         <v>114585</v>
       </c>
-      <c r="BA5" s="3">
+      <c r="BK5" s="3">
         <v>559867089965</v>
       </c>
-      <c r="BB5" s="3">
+      <c r="BL5" s="3">
         <v>114760.08</v>
       </c>
-      <c r="BC5" s="3">
+      <c r="BM5" s="3">
         <v>-0.05</v>
       </c>
+      <c r="BN5" s="3">
+        <v>4883000</v>
+      </c>
     </row>
-    <row r="6" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>46195</v>
       </c>
@@ -30730,158 +30850,191 @@
       <c r="E6" s="3">
         <v>-0.02</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
+        <v>37018000</v>
+      </c>
+      <c r="G6" s="2">
         <v>46195</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>87975</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>282419721184</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>87730.16</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>-0.09</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="M6" s="2">
         <v>46195</v>
       </c>
-      <c r="L6" s="3">
+      <c r="N6" s="3">
         <v>91815</v>
       </c>
-      <c r="M6" s="3">
+      <c r="O6" s="3">
         <v>392349402416</v>
       </c>
-      <c r="N6" s="3">
+      <c r="P6" s="3">
         <v>91164.24</v>
       </c>
-      <c r="O6" s="3">
+      <c r="Q6" s="3">
         <v>0.02</v>
       </c>
-      <c r="P6" s="2">
+      <c r="R6" s="3">
+        <v>4274000</v>
+      </c>
+      <c r="S6" s="2">
         <v>46195</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="T6" s="3">
         <v>98485</v>
       </c>
-      <c r="R6" s="3">
+      <c r="U6" s="3">
         <v>106236478383</v>
       </c>
-      <c r="S6" s="3">
+      <c r="V6" s="3">
         <v>98485.01</v>
       </c>
-      <c r="T6" s="3">
+      <c r="W6" s="3">
         <v>-0.11</v>
       </c>
-      <c r="U6" s="2">
+      <c r="X6" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="Y6" s="2">
         <v>46195</v>
       </c>
-      <c r="V6" s="3">
+      <c r="Z6" s="3">
         <v>99915</v>
       </c>
-      <c r="W6" s="3">
+      <c r="AA6" s="3">
         <v>73712348860</v>
       </c>
-      <c r="X6" s="3">
+      <c r="AB6" s="3">
         <v>99820.72</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="AC6" s="3">
         <v>-0.05</v>
       </c>
-      <c r="Z6" s="2">
-        <v>46195</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>106720</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>1346438398827</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>106499.95</v>
-      </c>
       <c r="AD6" s="3">
-        <v>-0.04</v>
+        <v>738000</v>
       </c>
       <c r="AE6" s="2">
         <v>46195</v>
       </c>
       <c r="AF6" s="3">
+        <v>106720</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>1346438398827</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>106499.95</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>12621000</v>
+      </c>
+      <c r="AK6" s="2">
+        <v>46195</v>
+      </c>
+      <c r="AL6" s="3">
         <v>54010</v>
       </c>
-      <c r="AG6" s="3">
+      <c r="AM6" s="3">
         <v>1156024200989</v>
       </c>
-      <c r="AH6" s="3">
+      <c r="AN6" s="3">
         <v>53998.89</v>
       </c>
-      <c r="AI6" s="3">
+      <c r="AO6" s="3">
         <v>0.02</v>
       </c>
-      <c r="AJ6" s="2">
+      <c r="AP6" s="3">
+        <v>21410000</v>
+      </c>
+      <c r="AQ6" s="2">
         <v>46195</v>
       </c>
-      <c r="AK6" s="3">
+      <c r="AR6" s="3">
         <v>51080</v>
       </c>
-      <c r="AL6" s="3">
+      <c r="AS6" s="3">
         <v>405549883061</v>
       </c>
-      <c r="AM6" s="3">
+      <c r="AT6" s="3">
         <v>51052.37</v>
       </c>
-      <c r="AN6" s="3">
+      <c r="AU6" s="3">
         <v>0.01</v>
       </c>
-      <c r="AO6" s="2">
+      <c r="AV6" s="3">
+        <v>7942000</v>
+      </c>
+      <c r="AW6" s="2">
         <v>46195</v>
       </c>
-      <c r="AP6" s="3">
+      <c r="AX6" s="3">
         <v>103360</v>
       </c>
-      <c r="AQ6" s="3">
+      <c r="AY6" s="3">
         <v>2182852294457</v>
       </c>
-      <c r="AR6" s="3">
+      <c r="AZ6" s="3">
         <v>103203.62</v>
       </c>
-      <c r="AS6" s="3">
+      <c r="BA6" s="3">
         <v>-0.04</v>
       </c>
-      <c r="AT6" s="2">
+      <c r="BB6" s="3">
+        <v>21114000</v>
+      </c>
+      <c r="BC6" s="2">
         <v>46195</v>
       </c>
-      <c r="AU6" s="3">
+      <c r="BD6" s="3">
         <v>50010</v>
       </c>
-      <c r="AV6" s="3">
+      <c r="BE6" s="3">
         <v>36890522655</v>
       </c>
-      <c r="AW6" s="3">
+      <c r="BF6" s="3">
         <v>49962.93</v>
       </c>
-      <c r="AX6" s="3">
+      <c r="BG6" s="3">
         <v>-0.04</v>
       </c>
-      <c r="AY6" s="2">
+      <c r="BH6" s="3">
+        <v>738000</v>
+      </c>
+      <c r="BI6" s="2">
         <v>46195</v>
       </c>
-      <c r="AZ6" s="3">
+      <c r="BJ6" s="3">
         <v>114700</v>
       </c>
-      <c r="BA6" s="3">
+      <c r="BK6" s="3">
         <v>560130097397</v>
       </c>
-      <c r="BB6" s="3">
+      <c r="BL6" s="3">
         <v>114656.38</v>
       </c>
-      <c r="BC6" s="3">
+      <c r="BM6" s="3">
         <v>-0.06</v>
       </c>
+      <c r="BN6" s="3">
+        <v>4881000</v>
+      </c>
     </row>
-    <row r="7" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>46192</v>
       </c>
@@ -30897,158 +31050,191 @@
       <c r="E7" s="3">
         <v>-0.04</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
+        <v>37180000</v>
+      </c>
+      <c r="G7" s="2">
         <v>46192</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>88725</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>283749430596</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>88036.07</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="M7" s="2">
         <v>46192</v>
       </c>
-      <c r="L7" s="3">
+      <c r="N7" s="3">
         <v>92715</v>
       </c>
-      <c r="M7" s="3">
+      <c r="O7" s="3">
         <v>395628709801</v>
       </c>
-      <c r="N7" s="3">
+      <c r="P7" s="3">
         <v>91799.11</v>
       </c>
-      <c r="O7" s="3">
+      <c r="Q7" s="3">
         <v>0.02</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="3">
+        <v>4274000</v>
+      </c>
+      <c r="S7" s="2">
         <v>46192</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="T7" s="3">
         <v>99000</v>
       </c>
-      <c r="R7" s="3">
+      <c r="U7" s="3">
         <v>106639132746</v>
       </c>
-      <c r="S7" s="3">
+      <c r="V7" s="3">
         <v>98549.61</v>
       </c>
-      <c r="T7" s="3">
+      <c r="W7" s="3">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="Y7" s="2">
         <v>46192</v>
       </c>
-      <c r="V7" s="3">
+      <c r="Z7" s="3">
         <v>100000</v>
       </c>
-      <c r="W7" s="3">
+      <c r="AA7" s="3">
         <v>73774147003</v>
       </c>
-      <c r="X7" s="3">
+      <c r="AB7" s="3">
         <v>99881.23</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="AC7" s="3">
         <v>0.03</v>
       </c>
-      <c r="Z7" s="2">
-        <v>46192</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>107060</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>1340539030525</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>106682.39</v>
-      </c>
       <c r="AD7" s="3">
-        <v>0.04</v>
+        <v>738000</v>
       </c>
       <c r="AE7" s="2">
         <v>46192</v>
       </c>
       <c r="AF7" s="3">
+        <v>107060</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>1340539030525</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>106682.39</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>12536000</v>
+      </c>
+      <c r="AK7" s="2">
+        <v>46192</v>
+      </c>
+      <c r="AL7" s="3">
         <v>54000</v>
       </c>
-      <c r="AG7" s="3">
+      <c r="AM7" s="3">
         <v>1152499605762</v>
       </c>
-      <c r="AH7" s="3">
+      <c r="AN7" s="3">
         <v>53994.59</v>
       </c>
-      <c r="AI7" s="3">
+      <c r="AO7" s="3">
         <v>0.03</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AP7" s="3">
+        <v>21350000</v>
+      </c>
+      <c r="AQ7" s="2">
         <v>46192</v>
       </c>
-      <c r="AK7" s="3">
+      <c r="AR7" s="3">
         <v>51090</v>
       </c>
-      <c r="AL7" s="3">
+      <c r="AS7" s="3">
         <v>405605197205</v>
       </c>
-      <c r="AM7" s="3">
+      <c r="AT7" s="3">
         <v>51063.95</v>
       </c>
-      <c r="AN7" s="3">
+      <c r="AU7" s="3">
         <v>0.03</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AV7" s="3">
+        <v>7942000</v>
+      </c>
+      <c r="AW7" s="2">
         <v>46192</v>
       </c>
-      <c r="AP7" s="3">
+      <c r="AX7" s="3">
         <v>103725</v>
       </c>
-      <c r="AQ7" s="3">
+      <c r="AY7" s="3">
         <v>2204799557577</v>
       </c>
-      <c r="AR7" s="3">
+      <c r="AZ7" s="3">
         <v>103384.12</v>
       </c>
-      <c r="AS7" s="3">
+      <c r="BA7" s="3">
         <v>-0.02</v>
       </c>
-      <c r="AT7" s="2">
+      <c r="BB7" s="3">
+        <v>21275000</v>
+      </c>
+      <c r="BC7" s="2">
         <v>46192</v>
       </c>
-      <c r="AU7" s="3">
+      <c r="BD7" s="3">
         <v>50045</v>
       </c>
-      <c r="AV7" s="3">
+      <c r="BE7" s="3">
         <v>34912137298</v>
       </c>
-      <c r="AW7" s="3">
+      <c r="BF7" s="3">
         <v>49987.16</v>
       </c>
-      <c r="AX7" s="3">
+      <c r="BG7" s="3">
         <v>0.05</v>
       </c>
-      <c r="AY7" s="2">
+      <c r="BH7" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI7" s="2">
         <v>46192</v>
       </c>
-      <c r="AZ7" s="3">
+      <c r="BJ7" s="3">
         <v>114825</v>
       </c>
-      <c r="BA7" s="3">
+      <c r="BK7" s="3">
         <v>561646513997</v>
       </c>
-      <c r="BB7" s="3">
+      <c r="BL7" s="3">
         <v>114757.24</v>
       </c>
-      <c r="BC7" s="3">
+      <c r="BM7" s="3">
         <v>-0.05</v>
       </c>
+      <c r="BN7" s="3">
+        <v>4891000</v>
+      </c>
     </row>
-    <row r="8" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>46191</v>
       </c>
@@ -31064,158 +31250,191 @@
       <c r="E8" s="3">
         <v>0.06</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
+        <v>36993000</v>
+      </c>
+      <c r="G8" s="2">
         <v>46191</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>88710</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>285243513344</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>88450.57</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>0.31</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="M8" s="2">
         <v>46191</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>93005</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>399044863199</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>92566.38</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>0.16</v>
       </c>
-      <c r="P8" s="2">
+      <c r="R8" s="3">
+        <v>4274000</v>
+      </c>
+      <c r="S8" s="2">
         <v>46191</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>99220</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>106767892372</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>98923.13</v>
       </c>
-      <c r="T8" s="3">
+      <c r="W8" s="3">
         <v>0.08</v>
       </c>
-      <c r="U8" s="2">
+      <c r="X8" s="3">
+        <v>1075000</v>
+      </c>
+      <c r="Y8" s="2">
         <v>46191</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>100030</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>74881307699</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AB8" s="3">
         <v>99964.97</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AC8" s="3">
         <v>0.04</v>
       </c>
-      <c r="Z8" s="2">
-        <v>46191</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>107150</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>1324333026659</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>106935.15</v>
-      </c>
       <c r="AD8" s="3">
-        <v>0.12</v>
+        <v>748000</v>
       </c>
       <c r="AE8" s="2">
         <v>46191</v>
       </c>
       <c r="AF8" s="3">
+        <v>107150</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>1324333026659</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>106935.15</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>12351000</v>
+      </c>
+      <c r="AK8" s="2">
+        <v>46191</v>
+      </c>
+      <c r="AL8" s="3">
         <v>53980</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AM8" s="3">
         <v>1174865160907</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AN8" s="3">
         <v>53981.25</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AO8" s="3">
         <v>0.03</v>
       </c>
-      <c r="AJ8" s="2">
+      <c r="AP8" s="3">
+        <v>21766000</v>
+      </c>
+      <c r="AQ8" s="2">
         <v>46191</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AR8" s="3">
         <v>51085</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AS8" s="3">
         <v>407826819504</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AT8" s="3">
         <v>51070.91</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AU8" s="3">
         <v>0.04</v>
       </c>
-      <c r="AO8" s="2">
+      <c r="AV8" s="3">
+        <v>7982000</v>
+      </c>
+      <c r="AW8" s="2">
         <v>46191</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AX8" s="3">
         <v>103815</v>
       </c>
-      <c r="AQ8" s="3">
+      <c r="AY8" s="3">
         <v>2172769690454</v>
       </c>
-      <c r="AR8" s="3">
+      <c r="AZ8" s="3">
         <v>103633.35</v>
       </c>
-      <c r="AS8" s="3">
+      <c r="BA8" s="3">
         <v>0.09</v>
       </c>
-      <c r="AT8" s="2">
+      <c r="BB8" s="3">
+        <v>20909000</v>
+      </c>
+      <c r="BC8" s="2">
         <v>46191</v>
       </c>
-      <c r="AU8" s="3">
+      <c r="BD8" s="3">
         <v>50055</v>
       </c>
-      <c r="AV8" s="3">
+      <c r="BE8" s="3">
         <v>34953615732</v>
       </c>
-      <c r="AW8" s="3">
+      <c r="BF8" s="3">
         <v>50017.39</v>
       </c>
-      <c r="AX8" s="3">
+      <c r="BG8" s="3">
         <v>0.06</v>
       </c>
-      <c r="AY8" s="2">
+      <c r="BH8" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI8" s="2">
         <v>46191</v>
       </c>
-      <c r="AZ8" s="3">
+      <c r="BJ8" s="3">
         <v>114950</v>
       </c>
-      <c r="BA8" s="3">
+      <c r="BK8" s="3">
         <v>564716957606</v>
       </c>
-      <c r="BB8" s="3">
+      <c r="BL8" s="3">
         <v>114832.65</v>
       </c>
-      <c r="BC8" s="3">
+      <c r="BM8" s="3">
         <v>-0.01</v>
       </c>
+      <c r="BN8" s="3">
+        <v>4911000</v>
+      </c>
     </row>
-    <row r="9" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>46190</v>
       </c>
@@ -31231,158 +31450,191 @@
       <c r="E9" s="3">
         <v>-0.04</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
+        <v>37005000</v>
+      </c>
+      <c r="G9" s="2">
         <v>46190</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>88360</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>283711723454</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>88916.31</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>-0.23</v>
       </c>
-      <c r="K9" s="2">
+      <c r="L9" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="M9" s="2">
         <v>46190</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>92495</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>394510540654</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>93365.67</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>-0.39</v>
       </c>
-      <c r="P9" s="2">
+      <c r="R9" s="3">
+        <v>4274000</v>
+      </c>
+      <c r="S9" s="2">
         <v>46190</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>98695</v>
       </c>
-      <c r="R9" s="3">
+      <c r="U9" s="3">
         <v>106391406120</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
         <v>99318.97</v>
       </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <v>-0.1</v>
       </c>
-      <c r="U9" s="2">
+      <c r="X9" s="3">
+        <v>1075000</v>
+      </c>
+      <c r="Y9" s="2">
         <v>46190</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>100040</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>74831397213</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AB9" s="3">
         <v>100108.7</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>-0.08</v>
       </c>
-      <c r="Z9" s="2">
-        <v>46190</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>106965</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>1318800351074</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>107224.76</v>
-      </c>
       <c r="AD9" s="3">
-        <v>-7.0000000000000007E-2</v>
+        <v>748000</v>
       </c>
       <c r="AE9" s="2">
         <v>46190</v>
       </c>
       <c r="AF9" s="3">
+        <v>106965</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>1318800351074</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>107224.76</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>12332000</v>
+      </c>
+      <c r="AK9" s="2">
+        <v>46190</v>
+      </c>
+      <c r="AL9" s="3">
         <v>53980</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AM9" s="3">
         <v>1174760512629</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AN9" s="3">
         <v>53977.08</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AO9" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ9" s="2">
+      <c r="AP9" s="3">
+        <v>21766000</v>
+      </c>
+      <c r="AQ9" s="2">
         <v>46190</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AR9" s="3">
         <v>51080</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AS9" s="3">
         <v>407842338724</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AT9" s="3">
         <v>51093.31</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AU9" s="3">
         <v>-0.02</v>
       </c>
-      <c r="AO9" s="2">
+      <c r="AV9" s="3">
+        <v>7984000</v>
+      </c>
+      <c r="AW9" s="2">
         <v>46190</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AX9" s="3">
         <v>103670</v>
       </c>
-      <c r="AQ9" s="3">
+      <c r="AY9" s="3">
         <v>2163514152815</v>
       </c>
-      <c r="AR9" s="3">
+      <c r="AZ9" s="3">
         <v>103915.52</v>
       </c>
-      <c r="AS9" s="3">
+      <c r="BA9" s="3">
         <v>-0.1</v>
       </c>
-      <c r="AT9" s="2">
+      <c r="BB9" s="3">
+        <v>20875000</v>
+      </c>
+      <c r="BC9" s="2">
         <v>46190</v>
       </c>
-      <c r="AU9" s="3">
+      <c r="BD9" s="3">
         <v>50010</v>
       </c>
-      <c r="AV9" s="3">
+      <c r="BE9" s="3">
         <v>34935376670</v>
       </c>
-      <c r="AW9" s="3">
+      <c r="BF9" s="3">
         <v>50076.81</v>
       </c>
-      <c r="AX9" s="3">
+      <c r="BG9" s="3">
         <v>-0.04</v>
       </c>
-      <c r="AY9" s="2">
+      <c r="BH9" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI9" s="2">
         <v>46190</v>
       </c>
-      <c r="AZ9" s="3">
+      <c r="BJ9" s="3">
         <v>114965</v>
       </c>
-      <c r="BA9" s="3">
+      <c r="BK9" s="3">
         <v>564202020935</v>
       </c>
-      <c r="BB9" s="3">
+      <c r="BL9" s="3">
         <v>114990.22</v>
       </c>
-      <c r="BC9" s="3">
+      <c r="BM9" s="3">
         <v>-0.03</v>
       </c>
+      <c r="BN9" s="3">
+        <v>4908000</v>
+      </c>
     </row>
-    <row r="10" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46189</v>
       </c>
@@ -31398,158 +31650,191 @@
       <c r="E10" s="3">
         <v>0.06</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
+        <v>37078000</v>
+      </c>
+      <c r="G10" s="2">
         <v>46189</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>88690</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>284111576178</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>88438.82</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-0.09</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="3">
+        <v>3208000</v>
+      </c>
+      <c r="M10" s="2">
         <v>46189</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>92775</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>402688068058</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>92304.76</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>0.21</v>
       </c>
-      <c r="P10" s="2">
+      <c r="R10" s="3">
+        <v>4343000</v>
+      </c>
+      <c r="S10" s="2">
         <v>46189</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>99080</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>106571075472</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>98968.75</v>
       </c>
-      <c r="T10" s="3">
+      <c r="W10" s="3">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="U10" s="2">
+      <c r="X10" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="Y10" s="2">
         <v>46189</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>100015</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>74677646631</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AB10" s="3">
         <v>100041.97</v>
       </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2">
-        <v>46189</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>107075</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>1306835864425</v>
-      </c>
       <c r="AC10" s="3">
-        <v>106941.32</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="3">
-        <v>0.02</v>
+        <v>747000</v>
       </c>
       <c r="AE10" s="2">
         <v>46189</v>
       </c>
       <c r="AF10" s="3">
+        <v>107075</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>1306835864425</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>106941.32</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>12215000</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>46189</v>
+      </c>
+      <c r="AL10" s="3">
         <v>53975</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AM10" s="3">
         <v>1174249728495</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AN10" s="3">
         <v>53972.27</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AO10" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ10" s="2">
+      <c r="AP10" s="3">
+        <v>21758000</v>
+      </c>
+      <c r="AQ10" s="2">
         <v>46189</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AR10" s="3">
         <v>51065</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AS10" s="3">
         <v>407913367809</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AT10" s="3">
         <v>51082.46</v>
       </c>
-      <c r="AN10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="2">
+      <c r="AU10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="3">
+        <v>7988000</v>
+      </c>
+      <c r="AW10" s="2">
         <v>46189</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AX10" s="3">
         <v>103755</v>
       </c>
-      <c r="AQ10" s="3">
+      <c r="AY10" s="3">
         <v>2159205179638</v>
       </c>
-      <c r="AR10" s="3">
+      <c r="AZ10" s="3">
         <v>103641.4</v>
       </c>
-      <c r="AS10" s="3">
+      <c r="BA10" s="3">
         <v>0.03</v>
       </c>
-      <c r="AT10" s="2">
+      <c r="BB10" s="3">
+        <v>20825000</v>
+      </c>
+      <c r="BC10" s="2">
         <v>46189</v>
       </c>
-      <c r="AU10" s="3">
+      <c r="BD10" s="3">
         <v>50015</v>
       </c>
-      <c r="AV10" s="3">
+      <c r="BE10" s="3">
         <v>34915463138</v>
       </c>
-      <c r="AW10" s="3">
+      <c r="BF10" s="3">
         <v>50050.68</v>
       </c>
-      <c r="AX10" s="3">
+      <c r="BG10" s="3">
         <v>-0.08</v>
       </c>
-      <c r="AY10" s="2">
+      <c r="BH10" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI10" s="2">
         <v>46189</v>
       </c>
-      <c r="AZ10" s="3">
+      <c r="BJ10" s="3">
         <v>114905</v>
       </c>
-      <c r="BA10" s="3">
+      <c r="BK10" s="3">
         <v>563551762502</v>
       </c>
-      <c r="BB10" s="3">
+      <c r="BL10" s="3">
         <v>114955.59</v>
       </c>
-      <c r="BC10" s="3">
+      <c r="BM10" s="3">
         <v>0.01</v>
       </c>
+      <c r="BN10" s="3">
+        <v>4905000</v>
+      </c>
     </row>
-    <row r="11" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>46188</v>
       </c>
@@ -31565,158 +31850,191 @@
       <c r="E11" s="3">
         <v>0.01</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
+        <v>37875000</v>
+      </c>
+      <c r="G11" s="2">
         <v>46188</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>87950</v>
       </c>
-      <c r="H11" s="3">
+      <c r="I11" s="3">
         <v>283735141320</v>
       </c>
-      <c r="I11" s="3">
+      <c r="J11" s="3">
         <v>88563.46</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="3">
+        <v>3218000</v>
+      </c>
+      <c r="M11" s="2">
         <v>46188</v>
       </c>
-      <c r="L11" s="3">
+      <c r="N11" s="3">
         <v>91680</v>
       </c>
-      <c r="M11" s="3">
+      <c r="O11" s="3">
         <v>405437176184</v>
       </c>
-      <c r="N11" s="3">
+      <c r="P11" s="3">
         <v>92721.18</v>
       </c>
-      <c r="O11" s="3">
+      <c r="Q11" s="3">
         <v>0.06</v>
       </c>
-      <c r="P11" s="2">
+      <c r="R11" s="3">
+        <v>4405000</v>
+      </c>
+      <c r="S11" s="2">
         <v>46188</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="T11" s="3">
         <v>98365</v>
       </c>
-      <c r="R11" s="3">
+      <c r="U11" s="3">
         <v>106061800434</v>
       </c>
-      <c r="S11" s="3">
+      <c r="V11" s="3">
         <v>98860</v>
       </c>
-      <c r="T11" s="3">
+      <c r="W11" s="3">
         <v>0.22</v>
       </c>
-      <c r="U11" s="2">
+      <c r="X11" s="3">
+        <v>1077000</v>
+      </c>
+      <c r="Y11" s="2">
         <v>46188</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Z11" s="3">
         <v>99770</v>
       </c>
-      <c r="W11" s="3">
+      <c r="AA11" s="3">
         <v>74170935602</v>
       </c>
-      <c r="X11" s="3">
+      <c r="AB11" s="3">
         <v>99970.08</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="AC11" s="3">
         <v>0.04</v>
       </c>
-      <c r="Z11" s="2">
-        <v>46188</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>106520</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>1313742245615</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>106986.15</v>
-      </c>
       <c r="AD11" s="3">
-        <v>0.08</v>
+        <v>743000</v>
       </c>
       <c r="AE11" s="2">
         <v>46188</v>
       </c>
       <c r="AF11" s="3">
+        <v>106520</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>1313742245615</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>106986.15</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>12310000</v>
+      </c>
+      <c r="AK11" s="2">
+        <v>46188</v>
+      </c>
+      <c r="AL11" s="3">
         <v>53970</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AM11" s="3">
         <v>1174367382010</v>
       </c>
-      <c r="AH11" s="3">
+      <c r="AN11" s="3">
         <v>53968.639999999999</v>
       </c>
-      <c r="AI11" s="3">
+      <c r="AO11" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ11" s="2">
+      <c r="AP11" s="3">
+        <v>21762000</v>
+      </c>
+      <c r="AQ11" s="2">
         <v>46188</v>
       </c>
-      <c r="AK11" s="3">
+      <c r="AR11" s="3">
         <v>51000</v>
       </c>
-      <c r="AL11" s="3">
+      <c r="AS11" s="3">
         <v>411225287046</v>
       </c>
-      <c r="AM11" s="3">
+      <c r="AT11" s="3">
         <v>51065.77</v>
       </c>
-      <c r="AN11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="2">
+      <c r="AU11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="3">
+        <v>8058000</v>
+      </c>
+      <c r="AW11" s="2">
         <v>46188</v>
       </c>
-      <c r="AP11" s="3">
+      <c r="AX11" s="3">
         <v>103265</v>
       </c>
-      <c r="AQ11" s="3">
+      <c r="AY11" s="3">
         <v>2158472332161</v>
       </c>
-      <c r="AR11" s="3">
+      <c r="AZ11" s="3">
         <v>103683.32</v>
       </c>
-      <c r="AS11" s="3">
+      <c r="BA11" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AT11" s="2">
+      <c r="BB11" s="3">
+        <v>20869000</v>
+      </c>
+      <c r="BC11" s="2">
         <v>46188</v>
       </c>
-      <c r="AU11" s="3">
+      <c r="BD11" s="3">
         <v>49960</v>
       </c>
-      <c r="AV11" s="3">
+      <c r="BE11" s="3">
         <v>34873235253</v>
       </c>
-      <c r="AW11" s="3">
+      <c r="BF11" s="3">
         <v>50022.15</v>
       </c>
-      <c r="AX11" s="3">
+      <c r="BG11" s="3">
         <v>-0.01</v>
       </c>
-      <c r="AY11" s="2">
+      <c r="BH11" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI11" s="2">
         <v>46188</v>
       </c>
-      <c r="AZ11" s="3">
+      <c r="BJ11" s="3">
         <v>114780</v>
       </c>
-      <c r="BA11" s="3">
+      <c r="BK11" s="3">
         <v>562821067228</v>
       </c>
-      <c r="BB11" s="3">
+      <c r="BL11" s="3">
         <v>114893.33</v>
       </c>
-      <c r="BC11" s="3">
+      <c r="BM11" s="3">
         <v>0.01</v>
       </c>
+      <c r="BN11" s="3">
+        <v>4905000</v>
+      </c>
     </row>
-    <row r="12" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>46185</v>
       </c>
@@ -31732,158 +32050,191 @@
       <c r="E12" s="3">
         <v>-0.06</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
+        <v>38550000</v>
+      </c>
+      <c r="G12" s="2">
         <v>46185</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>87300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>279854684703</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>88171.27</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>-0.25</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="3">
+        <v>3218000</v>
+      </c>
+      <c r="M12" s="2">
         <v>46185</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>90105</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>395909848385</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>92040.22</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>-0.39</v>
       </c>
-      <c r="P12" s="2">
+      <c r="R12" s="3">
+        <v>4408000</v>
+      </c>
+      <c r="S12" s="2">
         <v>46185</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="T12" s="3">
         <v>97680</v>
       </c>
-      <c r="R12" s="3">
+      <c r="U12" s="3">
         <v>105005267136</v>
       </c>
-      <c r="S12" s="3">
+      <c r="V12" s="3">
         <v>98478.92</v>
       </c>
-      <c r="T12" s="3">
+      <c r="W12" s="3">
         <v>-0.12</v>
       </c>
-      <c r="U12" s="2">
+      <c r="X12" s="3">
+        <v>1077000</v>
+      </c>
+      <c r="Y12" s="2">
         <v>46185</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Z12" s="3">
         <v>99575</v>
       </c>
-      <c r="W12" s="3">
+      <c r="AA12" s="3">
         <v>73943647327</v>
       </c>
-      <c r="X12" s="3">
+      <c r="AB12" s="3">
         <v>99826.29</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AC12" s="3">
         <v>-0.06</v>
       </c>
-      <c r="Z12" s="2">
-        <v>46185</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>106100</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>1283650802591</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>106721.55</v>
-      </c>
       <c r="AD12" s="3">
-        <v>-0.19</v>
+        <v>743000</v>
       </c>
       <c r="AE12" s="2">
         <v>46185</v>
       </c>
       <c r="AF12" s="3">
+        <v>106100</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>1283650802591</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>106721.55</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>-0.19</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>12112000</v>
+      </c>
+      <c r="AK12" s="2">
+        <v>46185</v>
+      </c>
+      <c r="AL12" s="3">
         <v>53955</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AM12" s="3">
         <v>1184058087745</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AN12" s="3">
         <v>53964.13</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AO12" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ12" s="2">
+      <c r="AP12" s="3">
+        <v>21948000</v>
+      </c>
+      <c r="AQ12" s="2">
         <v>46185</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AR12" s="3">
         <v>50990</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AS12" s="3">
         <v>412843743294</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AT12" s="3">
         <v>51033.17</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AU12" s="3">
         <v>-0.06</v>
       </c>
-      <c r="AO12" s="2">
+      <c r="AV12" s="3">
+        <v>8100000</v>
+      </c>
+      <c r="AW12" s="2">
         <v>46185</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AX12" s="3">
         <v>102860</v>
       </c>
-      <c r="AQ12" s="3">
+      <c r="AY12" s="3">
         <v>2164994462226</v>
       </c>
-      <c r="AR12" s="3">
+      <c r="AZ12" s="3">
         <v>103429.6</v>
       </c>
-      <c r="AS12" s="3">
+      <c r="BA12" s="3">
         <v>-0.16</v>
       </c>
-      <c r="AT12" s="2">
+      <c r="BB12" s="3">
+        <v>21079000</v>
+      </c>
+      <c r="BC12" s="2">
         <v>46185</v>
       </c>
-      <c r="AU12" s="3">
+      <c r="BD12" s="3">
         <v>49880</v>
       </c>
-      <c r="AV12" s="3">
+      <c r="BE12" s="3">
         <v>34786724137</v>
       </c>
-      <c r="AW12" s="3">
+      <c r="BF12" s="3">
         <v>49961.66</v>
       </c>
-      <c r="AX12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY12" s="2">
+      <c r="BG12" s="3">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI12" s="2">
         <v>46185</v>
       </c>
-      <c r="AZ12" s="3">
+      <c r="BJ12" s="3">
         <v>114510</v>
       </c>
-      <c r="BA12" s="3">
+      <c r="BK12" s="3">
         <v>563657394681</v>
       </c>
-      <c r="BB12" s="3">
+      <c r="BL12" s="3">
         <v>114744.36</v>
       </c>
-      <c r="BC12" s="3">
+      <c r="BM12" s="3">
         <v>0.03</v>
       </c>
+      <c r="BN12" s="3">
+        <v>4925000</v>
+      </c>
     </row>
-    <row r="13" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>46184</v>
       </c>
@@ -31899,158 +32250,191 @@
       <c r="E13" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
+        <v>38708000</v>
+      </c>
+      <c r="G13" s="2">
         <v>46184</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>87160</v>
       </c>
-      <c r="H13" s="3">
+      <c r="I13" s="3">
         <v>281144961029</v>
       </c>
-      <c r="I13" s="3">
+      <c r="J13" s="3">
         <v>86965.41</v>
       </c>
-      <c r="J13" s="3">
+      <c r="K13" s="3">
         <v>0.38</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="3">
+        <v>3218000</v>
+      </c>
+      <c r="M13" s="2">
         <v>46184</v>
       </c>
-      <c r="L13" s="3">
+      <c r="N13" s="3">
         <v>90275</v>
       </c>
-      <c r="M13" s="3">
+      <c r="O13" s="3">
         <v>399348791500</v>
       </c>
-      <c r="N13" s="3">
+      <c r="P13" s="3">
         <v>89816.21</v>
       </c>
-      <c r="O13" s="3">
+      <c r="Q13" s="3">
         <v>0.32</v>
       </c>
-      <c r="P13" s="2">
+      <c r="R13" s="3">
+        <v>4408000</v>
+      </c>
+      <c r="S13" s="2">
         <v>46184</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="T13" s="3">
         <v>97650</v>
       </c>
-      <c r="R13" s="3">
+      <c r="U13" s="3">
         <v>100516333520</v>
       </c>
-      <c r="S13" s="3">
+      <c r="V13" s="3">
         <v>97497.93</v>
       </c>
-      <c r="T13" s="3">
+      <c r="W13" s="3">
         <v>0.19</v>
       </c>
-      <c r="U13" s="2">
+      <c r="X13" s="3">
+        <v>1027000</v>
+      </c>
+      <c r="Y13" s="2">
         <v>46184</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Z13" s="3">
         <v>99540</v>
       </c>
-      <c r="W13" s="3">
+      <c r="AA13" s="3">
         <v>65023179853</v>
       </c>
-      <c r="X13" s="3">
+      <c r="AB13" s="3">
         <v>99520.39</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="AC13" s="3">
         <v>0.05</v>
       </c>
-      <c r="Z13" s="2">
-        <v>46184</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>106155</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>1286715560483</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>105981.74</v>
-      </c>
       <c r="AD13" s="3">
-        <v>0.11</v>
+        <v>653000</v>
       </c>
       <c r="AE13" s="2">
         <v>46184</v>
       </c>
       <c r="AF13" s="3">
+        <v>106155</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>1286715560483</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>105981.74</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>12114000</v>
+      </c>
+      <c r="AK13" s="2">
+        <v>46184</v>
+      </c>
+      <c r="AL13" s="3">
         <v>53950</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AM13" s="3">
         <v>1175361197544</v>
       </c>
-      <c r="AH13" s="3">
+      <c r="AN13" s="3">
         <v>53948.34</v>
       </c>
-      <c r="AI13" s="3">
+      <c r="AO13" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ13" s="2">
+      <c r="AP13" s="3">
+        <v>21788000</v>
+      </c>
+      <c r="AQ13" s="2">
         <v>46184</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AR13" s="3">
         <v>50980</v>
       </c>
-      <c r="AL13" s="3">
+      <c r="AS13" s="3">
         <v>413740856115</v>
       </c>
-      <c r="AM13" s="3">
+      <c r="AT13" s="3">
         <v>50968.36</v>
       </c>
-      <c r="AN13" s="3">
+      <c r="AU13" s="3">
         <v>0.04</v>
       </c>
-      <c r="AO13" s="2">
+      <c r="AV13" s="3">
+        <v>8116000</v>
+      </c>
+      <c r="AW13" s="2">
         <v>46184</v>
       </c>
-      <c r="AP13" s="3">
+      <c r="AX13" s="3">
         <v>102820</v>
       </c>
-      <c r="AQ13" s="3">
+      <c r="AY13" s="3">
         <v>2168273326932</v>
       </c>
-      <c r="AR13" s="3">
+      <c r="AZ13" s="3">
         <v>102708.59</v>
       </c>
-      <c r="AS13" s="3">
+      <c r="BA13" s="3">
         <v>0.15</v>
       </c>
-      <c r="AT13" s="2">
+      <c r="BB13" s="3">
+        <v>21065000</v>
+      </c>
+      <c r="BC13" s="2">
         <v>46184</v>
       </c>
-      <c r="AU13" s="3">
+      <c r="BD13" s="3">
         <v>49895</v>
       </c>
-      <c r="AV13" s="3">
+      <c r="BE13" s="3">
         <v>34807012865</v>
       </c>
-      <c r="AW13" s="3">
+      <c r="BF13" s="3">
         <v>49837.71</v>
       </c>
-      <c r="AX13" s="3">
+      <c r="BG13" s="3">
         <v>0.08</v>
       </c>
-      <c r="AY13" s="2">
+      <c r="BH13" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI13" s="2">
         <v>46184</v>
       </c>
-      <c r="AZ13" s="3">
+      <c r="BJ13" s="3">
         <v>114540</v>
       </c>
-      <c r="BA13" s="3">
+      <c r="BK13" s="3">
         <v>563921561560</v>
       </c>
-      <c r="BB13" s="3">
+      <c r="BL13" s="3">
         <v>114448.2</v>
       </c>
-      <c r="BC13" s="3">
+      <c r="BM13" s="3">
         <v>0.05</v>
       </c>
+      <c r="BN13" s="3">
+        <v>4925000</v>
+      </c>
     </row>
-    <row r="14" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>46183</v>
       </c>
@@ -32066,158 +32450,191 @@
       <c r="E14" s="3">
         <v>-0.13</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
+        <v>38822000</v>
+      </c>
+      <c r="G14" s="2">
         <v>46183</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>87595</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>286443898908</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>87366.36</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-0.24</v>
       </c>
-      <c r="K14" s="2">
+      <c r="L14" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="M14" s="2">
         <v>46183</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>91210</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>401147622093</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>90596.37</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-0.35</v>
       </c>
-      <c r="P14" s="2">
+      <c r="R14" s="3">
+        <v>4408000</v>
+      </c>
+      <c r="S14" s="2">
         <v>46183</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="T14" s="3">
         <v>97305</v>
       </c>
-      <c r="R14" s="3">
+      <c r="U14" s="3">
         <v>100393027455</v>
       </c>
-      <c r="S14" s="3">
+      <c r="V14" s="3">
         <v>97873.74</v>
       </c>
-      <c r="T14" s="3">
+      <c r="W14" s="3">
         <v>-0.23</v>
       </c>
-      <c r="U14" s="2">
+      <c r="X14" s="3">
+        <v>1027000</v>
+      </c>
+      <c r="Y14" s="2">
         <v>46183</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>99525</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <v>64957134408</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AB14" s="3">
         <v>99576.08</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AC14" s="3">
         <v>-0.04</v>
       </c>
-      <c r="Z14" s="2">
-        <v>46183</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>106095</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>1287750683809</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>106217.23</v>
-      </c>
       <c r="AD14" s="3">
-        <v>-0.06</v>
+        <v>653000</v>
       </c>
       <c r="AE14" s="2">
         <v>46183</v>
       </c>
       <c r="AF14" s="3">
+        <v>106095</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>1287750683809</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>106217.23</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>-0.06</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>12120000</v>
+      </c>
+      <c r="AK14" s="2">
+        <v>46183</v>
+      </c>
+      <c r="AL14" s="3">
         <v>53945</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AM14" s="3">
         <v>1185004528583</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AN14" s="3">
         <v>53945.35</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AO14" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ14" s="2">
+      <c r="AP14" s="3">
+        <v>21968000</v>
+      </c>
+      <c r="AQ14" s="2">
         <v>46183</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AR14" s="3">
         <v>50975</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AS14" s="3">
         <v>413661454625</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AT14" s="3">
         <v>50978.42</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="2">
+      <c r="AU14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="3">
+        <v>8116000</v>
+      </c>
+      <c r="AW14" s="2">
         <v>46183</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AX14" s="3">
         <v>103120</v>
       </c>
-      <c r="AQ14" s="3">
+      <c r="AY14" s="3">
         <v>2164649618497</v>
       </c>
-      <c r="AR14" s="3">
+      <c r="AZ14" s="3">
         <v>102932.51</v>
       </c>
-      <c r="AS14" s="3">
+      <c r="BA14" s="3">
         <v>-0.11</v>
       </c>
-      <c r="AT14" s="2">
+      <c r="BB14" s="3">
+        <v>21024000</v>
+      </c>
+      <c r="BC14" s="2">
         <v>46183</v>
       </c>
-      <c r="AU14" s="3">
+      <c r="BD14" s="3">
         <v>49850</v>
       </c>
-      <c r="AV14" s="3">
+      <c r="BE14" s="3">
         <v>34789258736</v>
       </c>
-      <c r="AW14" s="3">
+      <c r="BF14" s="3">
         <v>49866.78</v>
       </c>
-      <c r="AX14" s="3">
+      <c r="BG14" s="3">
         <v>0.06</v>
       </c>
-      <c r="AY14" s="2">
+      <c r="BH14" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI14" s="2">
         <v>46183</v>
       </c>
-      <c r="AZ14" s="3">
+      <c r="BJ14" s="3">
         <v>114450</v>
       </c>
-      <c r="BA14" s="3">
+      <c r="BK14" s="3">
         <v>565880166257</v>
       </c>
-      <c r="BB14" s="3">
+      <c r="BL14" s="3">
         <v>114501.84</v>
       </c>
-      <c r="BC14" s="3">
+      <c r="BM14" s="3">
         <v>0.03</v>
       </c>
+      <c r="BN14" s="3">
+        <v>4945000</v>
+      </c>
     </row>
-    <row r="15" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>46182</v>
       </c>
@@ -32233,158 +32650,191 @@
       <c r="E15" s="3">
         <v>0.09</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
+        <v>39096000</v>
+      </c>
+      <c r="G15" s="2">
         <v>46182</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>86880</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>284668233045</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>87463.79</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>0.15</v>
       </c>
-      <c r="K15" s="2">
+      <c r="L15" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="M15" s="2">
         <v>46182</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>89835</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>397546017912</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>91004.45</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>0.23</v>
       </c>
-      <c r="P15" s="2">
+      <c r="R15" s="3">
+        <v>4408000</v>
+      </c>
+      <c r="S15" s="2">
         <v>46182</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="T15" s="3">
         <v>97205</v>
       </c>
-      <c r="R15" s="3">
+      <c r="U15" s="3">
         <v>99807029871</v>
       </c>
-      <c r="S15" s="3">
+      <c r="V15" s="3">
         <v>97753.68</v>
       </c>
-      <c r="T15" s="3">
+      <c r="W15" s="3">
         <v>-0.46</v>
       </c>
-      <c r="U15" s="2">
+      <c r="X15" s="3">
+        <v>1027000</v>
+      </c>
+      <c r="Y15" s="2">
         <v>46182</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>99225</v>
       </c>
-      <c r="W15" s="3">
+      <c r="AA15" s="3">
         <v>63814659119</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AB15" s="3">
         <v>99474.94</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AC15" s="3">
         <v>0.05</v>
       </c>
-      <c r="Z15" s="2">
-        <v>46182</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>105815</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>1279907115524</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>106250.06</v>
-      </c>
       <c r="AD15" s="3">
-        <v>-0.15</v>
+        <v>643000</v>
       </c>
       <c r="AE15" s="2">
         <v>46182</v>
       </c>
       <c r="AF15" s="3">
+        <v>105815</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>1279907115524</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>106250.06</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>-0.15</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>12083000</v>
+      </c>
+      <c r="AK15" s="2">
+        <v>46182</v>
+      </c>
+      <c r="AL15" s="3">
         <v>53935</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AM15" s="3">
         <v>1191939879439</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AN15" s="3">
         <v>53942.3</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AO15" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ15" s="2">
+      <c r="AP15" s="3">
+        <v>22098000</v>
+      </c>
+      <c r="AQ15" s="2">
         <v>46182</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AR15" s="3">
         <v>50945</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AS15" s="3">
         <v>413354101178</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AT15" s="3">
         <v>50968.639999999999</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AU15" s="3">
         <v>0.01</v>
       </c>
-      <c r="AO15" s="2">
+      <c r="AV15" s="3">
+        <v>8116000</v>
+      </c>
+      <c r="AW15" s="2">
         <v>46182</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AX15" s="3">
         <v>102505</v>
       </c>
-      <c r="AQ15" s="3">
+      <c r="AY15" s="3">
         <v>2155208055271</v>
       </c>
-      <c r="AR15" s="3">
+      <c r="AZ15" s="3">
         <v>102960.88</v>
       </c>
-      <c r="AS15" s="3">
+      <c r="BA15" s="3">
         <v>0.15</v>
       </c>
-      <c r="AT15" s="2">
+      <c r="BB15" s="3">
+        <v>20998000</v>
+      </c>
+      <c r="BC15" s="2">
         <v>46182</v>
       </c>
-      <c r="AU15" s="3">
+      <c r="BD15" s="3">
         <v>49760</v>
       </c>
-      <c r="AV15" s="3">
+      <c r="BE15" s="3">
         <v>34731668213</v>
       </c>
-      <c r="AW15" s="3">
+      <c r="BF15" s="3">
         <v>49841.34</v>
       </c>
-      <c r="AX15" s="3">
+      <c r="BG15" s="3">
         <v>0.02</v>
       </c>
-      <c r="AY15" s="2">
+      <c r="BH15" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI15" s="2">
         <v>46182</v>
       </c>
-      <c r="AZ15" s="3">
+      <c r="BJ15" s="3">
         <v>114095</v>
       </c>
-      <c r="BA15" s="3">
+      <c r="BK15" s="3">
         <v>566980809171</v>
       </c>
-      <c r="BB15" s="3">
+      <c r="BL15" s="3">
         <v>114434.82</v>
       </c>
-      <c r="BC15" s="3">
+      <c r="BM15" s="3">
         <v>0.01</v>
       </c>
+      <c r="BN15" s="3">
+        <v>4965000</v>
+      </c>
     </row>
-    <row r="16" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>46181</v>
       </c>
@@ -32400,158 +32850,191 @@
       <c r="E16" s="3">
         <v>-0.2</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
+        <v>39128000</v>
+      </c>
+      <c r="G16" s="2">
         <v>46181</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>87545</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>286801084005</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
         <v>86921.600000000006</v>
       </c>
-      <c r="J16" s="3">
+      <c r="K16" s="3">
         <v>-0.05</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="M16" s="2">
         <v>46181</v>
       </c>
-      <c r="L16" s="3">
+      <c r="N16" s="3">
         <v>91270</v>
       </c>
-      <c r="M16" s="3">
+      <c r="O16" s="3">
         <v>388800471804</v>
       </c>
-      <c r="N16" s="3">
+      <c r="P16" s="3">
         <v>90187.39</v>
       </c>
-      <c r="O16" s="3">
+      <c r="Q16" s="3">
         <v>-0.39</v>
       </c>
-      <c r="P16" s="2">
+      <c r="R16" s="3">
+        <v>4258000</v>
+      </c>
+      <c r="S16" s="2">
         <v>46181</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="T16" s="3">
         <v>97905</v>
       </c>
-      <c r="R16" s="3">
+      <c r="U16" s="3">
         <v>101470733078</v>
       </c>
-      <c r="S16" s="3">
+      <c r="V16" s="3">
         <v>97183.09</v>
       </c>
-      <c r="T16" s="3">
+      <c r="W16" s="3">
         <v>0.02</v>
       </c>
-      <c r="U16" s="2">
+      <c r="X16" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="Y16" s="2">
         <v>46181</v>
       </c>
-      <c r="V16" s="3">
+      <c r="Z16" s="3">
         <v>99405</v>
       </c>
-      <c r="W16" s="3">
+      <c r="AA16" s="3">
         <v>64197460548</v>
       </c>
-      <c r="X16" s="3">
+      <c r="AB16" s="3">
         <v>99245.19</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="AC16" s="3">
         <v>-0.02</v>
       </c>
-      <c r="Z16" s="2">
-        <v>46181</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>106300</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>1283968166623</v>
-      </c>
-      <c r="AC16" s="3">
-        <v>105926.27</v>
-      </c>
       <c r="AD16" s="3">
-        <v>-0.11</v>
+        <v>646000</v>
       </c>
       <c r="AE16" s="2">
         <v>46181</v>
       </c>
       <c r="AF16" s="3">
+        <v>106300</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>1283968166623</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>105926.27</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>-0.11</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>12079000</v>
+      </c>
+      <c r="AK16" s="2">
+        <v>46181</v>
+      </c>
+      <c r="AL16" s="3">
         <v>53940</v>
       </c>
-      <c r="AG16" s="3">
+      <c r="AM16" s="3">
         <v>1193608832403</v>
       </c>
-      <c r="AH16" s="3">
+      <c r="AN16" s="3">
         <v>53938.81</v>
       </c>
-      <c r="AI16" s="3">
+      <c r="AO16" s="3">
         <v>-0.01</v>
       </c>
-      <c r="AJ16" s="2">
+      <c r="AP16" s="3">
+        <v>22130000</v>
+      </c>
+      <c r="AQ16" s="2">
         <v>46181</v>
       </c>
-      <c r="AK16" s="3">
+      <c r="AR16" s="3">
         <v>50965</v>
       </c>
-      <c r="AL16" s="3">
+      <c r="AS16" s="3">
         <v>413333507291</v>
       </c>
-      <c r="AM16" s="3">
+      <c r="AT16" s="3">
         <v>50930.77</v>
       </c>
-      <c r="AN16" s="3">
+      <c r="AU16" s="3">
         <v>0.03</v>
       </c>
-      <c r="AO16" s="2">
+      <c r="AV16" s="3">
+        <v>8110000</v>
+      </c>
+      <c r="AW16" s="2">
         <v>46181</v>
       </c>
-      <c r="AP16" s="3">
+      <c r="AX16" s="3">
         <v>103005</v>
       </c>
-      <c r="AQ16" s="3">
+      <c r="AY16" s="3">
         <v>2166746179134</v>
       </c>
-      <c r="AR16" s="3">
+      <c r="AZ16" s="3">
         <v>102638.73</v>
       </c>
-      <c r="AS16" s="3">
+      <c r="BA16" s="3">
         <v>-0.13</v>
       </c>
-      <c r="AT16" s="2">
+      <c r="BB16" s="3">
+        <v>21034000</v>
+      </c>
+      <c r="BC16" s="2">
         <v>46181</v>
       </c>
-      <c r="AU16" s="3">
+      <c r="BD16" s="3">
         <v>49835</v>
       </c>
-      <c r="AV16" s="3">
+      <c r="BE16" s="3">
         <v>34773127608</v>
       </c>
-      <c r="AW16" s="3">
+      <c r="BF16" s="3">
         <v>49758.84</v>
       </c>
-      <c r="AX16" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY16" s="2">
+      <c r="BG16" s="3">
+        <v>0</v>
+      </c>
+      <c r="BH16" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI16" s="2">
         <v>46181</v>
       </c>
-      <c r="AZ16" s="3">
+      <c r="BJ16" s="3">
         <v>114305</v>
       </c>
-      <c r="BA16" s="3">
+      <c r="BK16" s="3">
         <v>571483513363</v>
       </c>
-      <c r="BB16" s="3">
+      <c r="BL16" s="3">
         <v>114195.53</v>
       </c>
-      <c r="BC16" s="3">
+      <c r="BM16" s="3">
         <v>-0.09</v>
       </c>
+      <c r="BN16" s="3">
+        <v>4997000</v>
+      </c>
     </row>
-    <row r="17" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>46178</v>
       </c>
@@ -32567,158 +33050,191 @@
       <c r="E17" s="3">
         <v>-0.05</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
+        <v>38779000</v>
+      </c>
+      <c r="G17" s="2">
         <v>46178</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>88105</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>288242376600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>87572.85</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-0.03</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="M17" s="2">
         <v>46178</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>92630</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>391540706647</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>91310.59</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>-0.04</v>
       </c>
-      <c r="P17" s="2">
+      <c r="R17" s="3">
+        <v>4239000</v>
+      </c>
+      <c r="S17" s="2">
         <v>46178</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>98005</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>101198853463</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>97850.27</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>0.06</v>
       </c>
-      <c r="U17" s="2">
+      <c r="X17" s="3">
+        <v>1033000</v>
+      </c>
+      <c r="Y17" s="2">
         <v>46178</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>99390</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>64216136013</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>99376.87</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>0.03</v>
       </c>
-      <c r="Z17" s="2">
-        <v>46178</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>106530</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>1285810089140</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>106297.55</v>
-      </c>
       <c r="AD17" s="3">
-        <v>0</v>
+        <v>646000</v>
       </c>
       <c r="AE17" s="2">
         <v>46178</v>
       </c>
       <c r="AF17" s="3">
+        <v>106530</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>1285810089140</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>106297.55</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="3">
+        <v>12071000</v>
+      </c>
+      <c r="AK17" s="2">
+        <v>46178</v>
+      </c>
+      <c r="AL17" s="3">
         <v>53940</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AM17" s="3">
         <v>1190084017077</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AN17" s="3">
         <v>53936.23</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AO17" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ17" s="2">
+      <c r="AP17" s="3">
+        <v>22070000</v>
+      </c>
+      <c r="AQ17" s="2">
         <v>46178</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AR17" s="3">
         <v>50995</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AS17" s="3">
         <v>413369768014</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AT17" s="3">
         <v>50965.91</v>
       </c>
-      <c r="AN17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="2">
+      <c r="AU17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="3">
+        <v>8112000</v>
+      </c>
+      <c r="AW17" s="2">
         <v>46178</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AX17" s="3">
         <v>103275</v>
       </c>
-      <c r="AQ17" s="3">
+      <c r="AY17" s="3">
         <v>2154828510297</v>
       </c>
-      <c r="AR17" s="3">
+      <c r="AZ17" s="3">
         <v>103011.61</v>
       </c>
-      <c r="AS17" s="3">
+      <c r="BA17" s="3">
         <v>-0.01</v>
       </c>
-      <c r="AT17" s="2">
+      <c r="BB17" s="3">
+        <v>20872000</v>
+      </c>
+      <c r="BC17" s="2">
         <v>46178</v>
       </c>
-      <c r="AU17" s="3">
+      <c r="BD17" s="3">
         <v>49835</v>
       </c>
-      <c r="AV17" s="3">
+      <c r="BE17" s="3">
         <v>34780984457</v>
       </c>
-      <c r="AW17" s="3">
+      <c r="BF17" s="3">
         <v>49818.23</v>
       </c>
-      <c r="AX17" s="3">
+      <c r="BG17" s="3">
         <v>0.03</v>
       </c>
-      <c r="AY17" s="2">
+      <c r="BH17" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI17" s="2">
         <v>46178</v>
       </c>
-      <c r="AZ17" s="3">
+      <c r="BJ17" s="3">
         <v>114375</v>
       </c>
-      <c r="BA17" s="3">
+      <c r="BK17" s="3">
         <v>573959479407</v>
       </c>
-      <c r="BB17" s="3">
+      <c r="BL17" s="3">
         <v>114365.32</v>
       </c>
-      <c r="BC17" s="3">
+      <c r="BM17" s="3">
         <v>-0.05</v>
       </c>
+      <c r="BN17" s="3">
+        <v>5017000</v>
+      </c>
     </row>
-    <row r="18" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>46177</v>
       </c>
@@ -32734,158 +33250,191 @@
       <c r="E18" s="3">
         <v>0.08</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
+        <v>38676000</v>
+      </c>
+      <c r="G18" s="2">
         <v>46177</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>88825</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>290906161867</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>88012.94</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>0.1</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="M18" s="2">
         <v>46177</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>93815</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>382313729055</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>92366.29</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="P18" s="2">
+      <c r="R18" s="3">
+        <v>4075000</v>
+      </c>
+      <c r="S18" s="2">
         <v>46177</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>98820</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>101882839488</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>97965.98</v>
       </c>
-      <c r="T18" s="3">
+      <c r="W18" s="3">
         <v>0.04</v>
       </c>
-      <c r="U18" s="2">
+      <c r="X18" s="3">
+        <v>1033000</v>
+      </c>
+      <c r="Y18" s="2">
         <v>46177</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>99630</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>60383878111</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
         <v>99405.78</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>-0.02</v>
       </c>
-      <c r="Z18" s="2">
-        <v>46177</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>106990</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>1288539576364</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>106520.59</v>
-      </c>
       <c r="AD18" s="3">
-        <v>0.01</v>
+        <v>606000</v>
       </c>
       <c r="AE18" s="2">
         <v>46177</v>
       </c>
       <c r="AF18" s="3">
+        <v>106990</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>1288539576364</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>106520.59</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>12043000</v>
+      </c>
+      <c r="AK18" s="2">
+        <v>46177</v>
+      </c>
+      <c r="AL18" s="3">
         <v>53930</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AM18" s="3">
         <v>1182680886640</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AN18" s="3">
         <v>53923.15</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AO18" s="3">
         <v>0.03</v>
       </c>
-      <c r="AJ18" s="2">
+      <c r="AP18" s="3">
+        <v>21934000</v>
+      </c>
+      <c r="AQ18" s="2">
         <v>46177</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AR18" s="3">
         <v>51025</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AS18" s="3">
         <v>415303387840</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AT18" s="3">
         <v>50957.81</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AU18" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AO18" s="2">
+      <c r="AV18" s="3">
+        <v>8142000</v>
+      </c>
+      <c r="AW18" s="2">
         <v>46177</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AX18" s="3">
         <v>103740</v>
       </c>
-      <c r="AQ18" s="3">
+      <c r="AY18" s="3">
         <v>2165850556409</v>
       </c>
-      <c r="AR18" s="3">
+      <c r="AZ18" s="3">
         <v>103240.15</v>
       </c>
-      <c r="AS18" s="3">
+      <c r="BA18" s="3">
         <v>0.03</v>
       </c>
-      <c r="AT18" s="2">
+      <c r="BB18" s="3">
+        <v>20881000</v>
+      </c>
+      <c r="BC18" s="2">
         <v>46177</v>
       </c>
-      <c r="AU18" s="3">
+      <c r="BD18" s="3">
         <v>49890</v>
       </c>
-      <c r="AV18" s="3">
+      <c r="BE18" s="3">
         <v>34849990335</v>
       </c>
-      <c r="AW18" s="3">
+      <c r="BF18" s="3">
         <v>49829.49</v>
       </c>
-      <c r="AX18" s="3">
+      <c r="BG18" s="3">
         <v>0.01</v>
       </c>
-      <c r="AY18" s="2">
+      <c r="BH18" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI18" s="2">
         <v>46177</v>
       </c>
-      <c r="AZ18" s="3">
+      <c r="BJ18" s="3">
         <v>114720</v>
       </c>
-      <c r="BA18" s="3">
+      <c r="BK18" s="3">
         <v>576491613801</v>
       </c>
-      <c r="BB18" s="3">
+      <c r="BL18" s="3">
         <v>114402.93</v>
       </c>
-      <c r="BC18" s="3">
+      <c r="BM18" s="3">
         <v>-0.02</v>
       </c>
+      <c r="BN18" s="3">
+        <v>5027000</v>
+      </c>
     </row>
-    <row r="19" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>46175</v>
       </c>
@@ -32901,158 +33450,191 @@
       <c r="E19" s="3">
         <v>-0.08</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
+        <v>38724000</v>
+      </c>
+      <c r="G19" s="2">
         <v>46175</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>88565</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>289113244587</v>
       </c>
-      <c r="I19" s="3">
+      <c r="J19" s="3">
         <v>88826.31</v>
       </c>
-      <c r="J19" s="3">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2">
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>3262000</v>
+      </c>
+      <c r="M19" s="2">
         <v>46175</v>
       </c>
-      <c r="L19" s="3">
+      <c r="N19" s="3">
         <v>93495</v>
       </c>
-      <c r="M19" s="3">
+      <c r="O19" s="3">
         <v>360734418185</v>
       </c>
-      <c r="N19" s="3">
+      <c r="P19" s="3">
         <v>93819.32</v>
       </c>
-      <c r="O19" s="3">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2">
+      <c r="Q19" s="3">
+        <v>0</v>
+      </c>
+      <c r="R19" s="3">
+        <v>3856000</v>
+      </c>
+      <c r="S19" s="2">
         <v>46175</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="T19" s="3">
         <v>98365</v>
       </c>
-      <c r="R19" s="3">
+      <c r="U19" s="3">
         <v>101921072390</v>
       </c>
-      <c r="S19" s="3">
+      <c r="V19" s="3">
         <v>98628.11</v>
       </c>
-      <c r="T19" s="3">
+      <c r="W19" s="3">
         <v>0.19</v>
       </c>
-      <c r="U19" s="2">
+      <c r="X19" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="Y19" s="2">
         <v>46175</v>
       </c>
-      <c r="V19" s="3">
+      <c r="Z19" s="3">
         <v>99580</v>
       </c>
-      <c r="W19" s="3">
+      <c r="AA19" s="3">
         <v>61233506009</v>
       </c>
-      <c r="X19" s="3">
+      <c r="AB19" s="3">
         <v>99643.36</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="AC19" s="3">
         <v>-0.01</v>
       </c>
-      <c r="Z19" s="2">
-        <v>46175</v>
-      </c>
-      <c r="AA19" s="3">
-        <v>106885</v>
-      </c>
-      <c r="AB19" s="3">
-        <v>1281803565954</v>
-      </c>
-      <c r="AC19" s="3">
-        <v>106994.9</v>
-      </c>
       <c r="AD19" s="3">
-        <v>0</v>
+        <v>615000</v>
       </c>
       <c r="AE19" s="2">
         <v>46175</v>
       </c>
       <c r="AF19" s="3">
+        <v>106885</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>1281803565954</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>106994.9</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>11992000</v>
+      </c>
+      <c r="AK19" s="2">
+        <v>46175</v>
+      </c>
+      <c r="AL19" s="3">
         <v>53925</v>
       </c>
-      <c r="AG19" s="3">
+      <c r="AM19" s="3">
         <v>1175164788582</v>
       </c>
-      <c r="AH19" s="3">
+      <c r="AN19" s="3">
         <v>53919.98</v>
       </c>
-      <c r="AI19" s="3">
+      <c r="AO19" s="3">
         <v>0.02</v>
       </c>
-      <c r="AJ19" s="2">
+      <c r="AP19" s="3">
+        <v>21798000</v>
+      </c>
+      <c r="AQ19" s="2">
         <v>46175</v>
       </c>
-      <c r="AK19" s="3">
+      <c r="AR19" s="3">
         <v>51030</v>
       </c>
-      <c r="AL19" s="3">
+      <c r="AS19" s="3">
         <v>414759532182</v>
       </c>
-      <c r="AM19" s="3">
+      <c r="AT19" s="3">
         <v>51007.54</v>
       </c>
-      <c r="AN19" s="3">
+      <c r="AU19" s="3">
         <v>0.03</v>
       </c>
-      <c r="AO19" s="2">
+      <c r="AV19" s="3">
+        <v>8132000</v>
+      </c>
+      <c r="AW19" s="2">
         <v>46175</v>
       </c>
-      <c r="AP19" s="3">
+      <c r="AX19" s="3">
         <v>103600</v>
       </c>
-      <c r="AQ19" s="3">
+      <c r="AY19" s="3">
         <v>2156854948438</v>
       </c>
-      <c r="AR19" s="3">
+      <c r="AZ19" s="3">
         <v>103723.51</v>
       </c>
-      <c r="AS19" s="3">
+      <c r="BA19" s="3">
         <v>0.02</v>
       </c>
-      <c r="AT19" s="2">
+      <c r="BB19" s="3">
+        <v>20818000</v>
+      </c>
+      <c r="BC19" s="2">
         <v>46175</v>
       </c>
-      <c r="AU19" s="3">
+      <c r="BD19" s="3">
         <v>49915</v>
       </c>
-      <c r="AV19" s="3">
+      <c r="BE19" s="3">
         <v>34832570779</v>
       </c>
-      <c r="AW19" s="3">
+      <c r="BF19" s="3">
         <v>49928.35</v>
       </c>
-      <c r="AX19" s="3">
+      <c r="BG19" s="3">
         <v>-0.08</v>
       </c>
-      <c r="AY19" s="2">
+      <c r="BH19" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI19" s="2">
         <v>46175</v>
       </c>
-      <c r="AZ19" s="3">
+      <c r="BJ19" s="3">
         <v>114535</v>
       </c>
-      <c r="BA19" s="3">
+      <c r="BK19" s="3">
         <v>578521042541</v>
       </c>
-      <c r="BB19" s="3">
+      <c r="BL19" s="3">
         <v>114679.06</v>
       </c>
-      <c r="BC19" s="3">
+      <c r="BM19" s="3">
         <v>0.04</v>
       </c>
+      <c r="BN19" s="3">
+        <v>5047000</v>
+      </c>
     </row>
-    <row r="20" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>46174</v>
       </c>
@@ -33068,158 +33650,191 @@
       <c r="E20" s="3">
         <v>-0.09</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
+        <v>38692000</v>
+      </c>
+      <c r="G20" s="2">
         <v>46174</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>89555</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>292952075163</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>88630.67</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="3">
+        <v>3262000</v>
+      </c>
+      <c r="M20" s="2">
         <v>46174</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>95530</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>373548104112</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>93551.46</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-0.06</v>
       </c>
-      <c r="P20" s="2">
+      <c r="R20" s="3">
+        <v>3896000</v>
+      </c>
+      <c r="S20" s="2">
         <v>46174</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>99035</v>
       </c>
-      <c r="R20" s="3">
+      <c r="U20" s="3">
         <v>102788046468</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
         <v>98284.54</v>
       </c>
-      <c r="T20" s="3">
+      <c r="W20" s="3">
         <v>0.08</v>
       </c>
-      <c r="U20" s="2">
+      <c r="X20" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="Y20" s="2">
         <v>46174</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Z20" s="3">
         <v>99720</v>
       </c>
-      <c r="W20" s="3">
+      <c r="AA20" s="3">
         <v>60358572459</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AB20" s="3">
         <v>99566.68</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AC20" s="3">
         <v>0.01</v>
       </c>
-      <c r="Z20" s="2">
-        <v>46174</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>107540</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1291688910209</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>106888.22</v>
-      </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>605000</v>
       </c>
       <c r="AE20" s="2">
         <v>46174</v>
       </c>
       <c r="AF20" s="3">
+        <v>107540</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>1291688910209</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>106888.22</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>12012000</v>
+      </c>
+      <c r="AK20" s="2">
+        <v>46174</v>
+      </c>
+      <c r="AL20" s="3">
         <v>53915</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AM20" s="3">
         <v>1154806469431</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AN20" s="3">
         <v>53911.59</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AO20" s="3">
         <v>0.02</v>
       </c>
-      <c r="AJ20" s="2">
+      <c r="AP20" s="3">
+        <v>21422000</v>
+      </c>
+      <c r="AQ20" s="2">
         <v>46174</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AR20" s="3">
         <v>51035</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AS20" s="3">
         <v>414086777212</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AT20" s="3">
         <v>51003.39</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AU20" s="3">
         <v>0.05</v>
       </c>
-      <c r="AO20" s="2">
+      <c r="AV20" s="3">
+        <v>8114000</v>
+      </c>
+      <c r="AW20" s="2">
         <v>46174</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AX20" s="3">
         <v>104165</v>
       </c>
-      <c r="AQ20" s="3">
+      <c r="AY20" s="3">
         <v>2156781575624</v>
       </c>
-      <c r="AR20" s="3">
+      <c r="AZ20" s="3">
         <v>103605.29</v>
       </c>
-      <c r="AS20" s="3">
+      <c r="BA20" s="3">
         <v>-0.01</v>
       </c>
-      <c r="AT20" s="2">
+      <c r="BB20" s="3">
+        <v>20688000</v>
+      </c>
+      <c r="BC20" s="2">
         <v>46174</v>
       </c>
-      <c r="AU20" s="3">
+      <c r="BD20" s="3">
         <v>49985</v>
       </c>
-      <c r="AV20" s="3">
+      <c r="BE20" s="3">
         <v>34885007842</v>
       </c>
-      <c r="AW20" s="3">
+      <c r="BF20" s="3">
         <v>49903.4</v>
       </c>
-      <c r="AX20" s="3">
+      <c r="BG20" s="3">
         <v>0.02</v>
       </c>
-      <c r="AY20" s="2">
+      <c r="BH20" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI20" s="2">
         <v>46174</v>
       </c>
-      <c r="AZ20" s="3">
+      <c r="BJ20" s="3">
         <v>114815</v>
       </c>
-      <c r="BA20" s="3">
+      <c r="BK20" s="3">
         <v>581795806621</v>
       </c>
-      <c r="BB20" s="3">
+      <c r="BL20" s="3">
         <v>114626.72</v>
       </c>
-      <c r="BC20" s="3">
+      <c r="BM20" s="3">
         <v>-0.08</v>
       </c>
+      <c r="BN20" s="3">
+        <v>5067000</v>
+      </c>
     </row>
-    <row r="21" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>46171</v>
       </c>
@@ -33235,158 +33850,191 @@
       <c r="E21" s="3">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
+        <v>39117000</v>
+      </c>
+      <c r="G21" s="2">
         <v>46171</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>88730</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>291341786269</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>89807.5</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="3">
+        <v>3282000</v>
+      </c>
+      <c r="M21" s="2">
         <v>46171</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>93685</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>352000498025</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>95879.9</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-0.36</v>
       </c>
-      <c r="P21" s="2">
+      <c r="R21" s="3">
+        <v>3752000</v>
+      </c>
+      <c r="S21" s="2">
         <v>46171</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="T21" s="3">
         <v>98505</v>
       </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <v>102116449680</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
         <v>99120.58</v>
       </c>
-      <c r="T21" s="3">
+      <c r="W21" s="3">
         <v>-0.09</v>
       </c>
-      <c r="U21" s="2">
+      <c r="X21" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="Y21" s="2">
         <v>46171</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <v>99600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="AA21" s="3">
         <v>59265974285</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AB21" s="3">
         <v>99766.24</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AC21" s="3">
         <v>-0.05</v>
       </c>
-      <c r="Z21" s="2">
-        <v>46171</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>106995</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>1284173932754</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>107533.21</v>
-      </c>
       <c r="AD21" s="3">
-        <v>0.01</v>
+        <v>595000</v>
       </c>
       <c r="AE21" s="2">
         <v>46171</v>
       </c>
       <c r="AF21" s="3">
-        <v>53900</v>
+        <v>106995</v>
       </c>
       <c r="AG21" s="3">
-        <v>1174775496440</v>
+        <v>1284173932754</v>
       </c>
       <c r="AH21" s="3">
-        <v>53907.5</v>
+        <v>107533.21</v>
       </c>
       <c r="AI21" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ21" s="2">
+      <c r="AJ21" s="3">
+        <v>12006000</v>
+      </c>
+      <c r="AK21" s="2">
         <v>46171</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
+        <v>53900</v>
+      </c>
+      <c r="AM21" s="3">
+        <v>1174775496440</v>
+      </c>
+      <c r="AN21" s="3">
+        <v>53907.5</v>
+      </c>
+      <c r="AO21" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="AP21" s="3">
+        <v>21798000</v>
+      </c>
+      <c r="AQ21" s="2">
+        <v>46171</v>
+      </c>
+      <c r="AR21" s="3">
         <v>51035</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AS21" s="3">
         <v>413864911584</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AT21" s="3">
         <v>51033.62</v>
       </c>
-      <c r="AN21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="2">
+      <c r="AU21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="3">
+        <v>8114000</v>
+      </c>
+      <c r="AW21" s="2">
         <v>46171</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AX21" s="3">
         <v>103635</v>
       </c>
-      <c r="AQ21" s="3">
+      <c r="AY21" s="3">
         <v>2117081042662</v>
       </c>
-      <c r="AR21" s="3">
+      <c r="AZ21" s="3">
         <v>104252.78</v>
       </c>
-      <c r="AS21" s="3">
+      <c r="BA21" s="3">
         <v>-0.08</v>
       </c>
-      <c r="AT21" s="2">
+      <c r="BB21" s="3">
+        <v>20420000</v>
+      </c>
+      <c r="BC21" s="2">
         <v>46171</v>
       </c>
-      <c r="AU21" s="3">
+      <c r="BD21" s="3">
         <v>49905</v>
       </c>
-      <c r="AV21" s="3">
+      <c r="BE21" s="3">
         <v>34839914317</v>
       </c>
-      <c r="AW21" s="3">
+      <c r="BF21" s="3">
         <v>49978.52</v>
       </c>
-      <c r="AX21" s="3">
+      <c r="BG21" s="3">
         <v>0.01</v>
       </c>
-      <c r="AY21" s="2">
+      <c r="BH21" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI21" s="2">
         <v>46171</v>
       </c>
-      <c r="AZ21" s="3">
+      <c r="BJ21" s="3">
         <v>114675</v>
       </c>
-      <c r="BA21" s="3">
+      <c r="BK21" s="3">
         <v>583230154297</v>
       </c>
-      <c r="BB21" s="3">
+      <c r="BL21" s="3">
         <v>114820.57</v>
       </c>
-      <c r="BC21" s="3">
-        <v>0</v>
+      <c r="BM21" s="3">
+        <v>0</v>
+      </c>
+      <c r="BN21" s="3">
+        <v>5087000</v>
       </c>
     </row>
-    <row r="22" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>46170</v>
       </c>
@@ -33402,158 +34050,191 @@
       <c r="E22" s="3">
         <v>-0.11</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
+        <v>39168000</v>
+      </c>
+      <c r="G22" s="2">
         <v>46170</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>89245</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>292066640697</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>88769.59</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>-0.04</v>
       </c>
-      <c r="K22" s="2">
+      <c r="L22" s="3">
+        <v>3282000</v>
+      </c>
+      <c r="M22" s="2">
         <v>46170</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>94515</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>353480932024</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>93816.76</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="P22" s="2">
+      <c r="R22" s="3">
+        <v>3756000</v>
+      </c>
+      <c r="S22" s="2">
         <v>46170</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="T22" s="3">
         <v>98895</v>
       </c>
-      <c r="R22" s="3">
+      <c r="U22" s="3">
         <v>97660920922</v>
       </c>
-      <c r="S22" s="3">
+      <c r="V22" s="3">
         <v>98472.95</v>
       </c>
-      <c r="T22" s="3">
+      <c r="W22" s="3">
         <v>0.03</v>
       </c>
-      <c r="U22" s="2">
+      <c r="X22" s="3">
+        <v>989000</v>
+      </c>
+      <c r="Y22" s="2">
         <v>46170</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>99820</v>
       </c>
-      <c r="W22" s="3">
+      <c r="AA22" s="3">
         <v>59335065774</v>
       </c>
-      <c r="X22" s="3">
+      <c r="AB22" s="3">
         <v>99606.68</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AC22" s="3">
         <v>-0.01</v>
       </c>
-      <c r="Z22" s="2">
-        <v>46170</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>107255</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>1296081259431</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>106961.01</v>
-      </c>
       <c r="AD22" s="3">
-        <v>0.03</v>
+        <v>595000</v>
       </c>
       <c r="AE22" s="2">
         <v>46170</v>
       </c>
       <c r="AF22" s="3">
+        <v>107255</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>1296081259431</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>106961.01</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>12100000</v>
+      </c>
+      <c r="AK22" s="2">
+        <v>46170</v>
+      </c>
+      <c r="AL22" s="3">
         <v>53890</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AM22" s="3">
         <v>1194096410676</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AN22" s="3">
         <v>53893.73</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AO22" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ22" s="2">
+      <c r="AP22" s="3">
+        <v>22158000</v>
+      </c>
+      <c r="AQ22" s="2">
         <v>46170</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AR22" s="3">
         <v>51050</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AS22" s="3">
         <v>419516712996</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AT22" s="3">
         <v>51006.27</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AU22" s="3">
         <v>0.06</v>
       </c>
-      <c r="AO22" s="2">
+      <c r="AV22" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="AW22" s="2">
         <v>46170</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AX22" s="3">
         <v>103970</v>
       </c>
-      <c r="AQ22" s="3">
+      <c r="AY22" s="3">
         <v>2111858473530</v>
       </c>
-      <c r="AR22" s="3">
+      <c r="AZ22" s="3">
         <v>103676.84</v>
       </c>
-      <c r="AS22" s="3">
+      <c r="BA22" s="3">
         <v>-0.04</v>
       </c>
-      <c r="AT22" s="2">
+      <c r="BB22" s="3">
+        <v>20343000</v>
+      </c>
+      <c r="BC22" s="2">
         <v>46170</v>
       </c>
-      <c r="AU22" s="3">
+      <c r="BD22" s="3">
         <v>50000</v>
       </c>
-      <c r="AV22" s="3">
+      <c r="BE22" s="3">
         <v>34874982044</v>
       </c>
-      <c r="AW22" s="3">
+      <c r="BF22" s="3">
         <v>49913.919999999998</v>
       </c>
-      <c r="AX22" s="3">
+      <c r="BG22" s="3">
         <v>-0.02</v>
       </c>
-      <c r="AY22" s="2">
+      <c r="BH22" s="3">
+        <v>698000</v>
+      </c>
+      <c r="BI22" s="2">
         <v>46170</v>
       </c>
-      <c r="AZ22" s="3">
+      <c r="BJ22" s="3">
         <v>114800</v>
       </c>
-      <c r="BA22" s="3">
+      <c r="BK22" s="3">
         <v>585656630699</v>
       </c>
-      <c r="BB22" s="3">
+      <c r="BL22" s="3">
         <v>114651.1</v>
       </c>
-      <c r="BC22" s="3">
+      <c r="BM22" s="3">
         <v>0.02</v>
       </c>
+      <c r="BN22" s="3">
+        <v>5102000</v>
+      </c>
     </row>
-    <row r="23" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>46169</v>
       </c>
@@ -33569,158 +34250,191 @@
       <c r="E23" s="3">
         <v>0.06</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
+        <v>38987000</v>
+      </c>
+      <c r="G23" s="2">
         <v>46169</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>89160</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>291499771922</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>88990.45</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="K23" s="2">
+      <c r="L23" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="M23" s="2">
         <v>46169</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>94025</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>347347408434</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>94111</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>0.43</v>
       </c>
-      <c r="P23" s="2">
+      <c r="R23" s="3">
+        <v>3689000</v>
+      </c>
+      <c r="S23" s="2">
         <v>46169</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>99055</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>92665206858</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>98747.14</v>
       </c>
-      <c r="T23" s="3">
+      <c r="W23" s="3">
         <v>0.15</v>
       </c>
-      <c r="U23" s="2">
+      <c r="X23" s="3">
+        <v>936000</v>
+      </c>
+      <c r="Y23" s="2">
         <v>46169</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>99875</v>
       </c>
-      <c r="W23" s="3">
+      <c r="AA23" s="3">
         <v>62314337395</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AB23" s="3">
         <v>99722.8</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AC23" s="3">
         <v>0.1</v>
       </c>
-      <c r="Z23" s="2">
-        <v>46169</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>107205</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>1293430697216</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>107114.15</v>
-      </c>
       <c r="AD23" s="3">
-        <v>0.13</v>
+        <v>624000</v>
       </c>
       <c r="AE23" s="2">
         <v>46169</v>
       </c>
       <c r="AF23" s="3">
+        <v>107205</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>1293430697216</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>107114.15</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>12063000</v>
+      </c>
+      <c r="AK23" s="2">
+        <v>46169</v>
+      </c>
+      <c r="AL23" s="3">
         <v>53890</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AM23" s="3">
         <v>1181295773075</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AN23" s="3">
         <v>53890.080000000002</v>
       </c>
-      <c r="AI23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="2">
+      <c r="AO23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="3">
+        <v>21922000</v>
+      </c>
+      <c r="AQ23" s="2">
         <v>46169</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AR23" s="3">
         <v>51060</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AS23" s="3">
         <v>419701437035</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AT23" s="3">
         <v>51036.1</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AU23" s="3">
         <v>0.03</v>
       </c>
-      <c r="AO23" s="2">
+      <c r="AV23" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="AW23" s="2">
         <v>46169</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AX23" s="3">
         <v>103925</v>
       </c>
-      <c r="AQ23" s="3">
+      <c r="AY23" s="3">
         <v>2115860281184</v>
       </c>
-      <c r="AR23" s="3">
+      <c r="AZ23" s="3">
         <v>103812.54</v>
       </c>
-      <c r="AS23" s="3">
+      <c r="BA23" s="3">
         <v>0.15</v>
       </c>
-      <c r="AT23" s="2">
+      <c r="BB23" s="3">
+        <v>20362000</v>
+      </c>
+      <c r="BC23" s="2">
         <v>46169</v>
       </c>
-      <c r="AU23" s="3">
+      <c r="BD23" s="3">
         <v>50025</v>
       </c>
-      <c r="AV23" s="3">
+      <c r="BE23" s="3">
         <v>35113760175</v>
       </c>
-      <c r="AW23" s="3">
+      <c r="BF23" s="3">
         <v>49964.160000000003</v>
       </c>
-      <c r="AX23" s="3">
+      <c r="BG23" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AY23" s="2">
+      <c r="BH23" s="3">
+        <v>702000</v>
+      </c>
+      <c r="BI23" s="2">
         <v>46169</v>
       </c>
-      <c r="AZ23" s="3">
+      <c r="BJ23" s="3">
         <v>114945</v>
       </c>
-      <c r="BA23" s="3">
+      <c r="BK23" s="3">
         <v>586398963164</v>
       </c>
-      <c r="BB23" s="3">
+      <c r="BL23" s="3">
         <v>114789.62</v>
       </c>
-      <c r="BC23" s="3">
+      <c r="BM23" s="3">
         <v>0.01</v>
       </c>
+      <c r="BN23" s="3">
+        <v>5102000</v>
+      </c>
     </row>
-    <row r="24" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>46168</v>
       </c>
@@ -33736,158 +34450,191 @@
       <c r="E24" s="3">
         <v>0.04</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
+        <v>38851000</v>
+      </c>
+      <c r="G24" s="2">
         <v>46168</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>88550</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>289931788265</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>89116.41</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>0.05</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="M24" s="2">
         <v>46168</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>93490</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>344334438004</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>94157.61</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="P24" s="2">
+      <c r="R24" s="3">
+        <v>3689000</v>
+      </c>
+      <c r="S24" s="2">
         <v>46168</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="T24" s="3">
         <v>98510</v>
       </c>
-      <c r="R24" s="3">
+      <c r="U24" s="3">
         <v>91562681939</v>
       </c>
-      <c r="S24" s="3">
+      <c r="V24" s="3">
         <v>99001.29</v>
       </c>
-      <c r="T24" s="3">
+      <c r="W24" s="3">
         <v>0.05</v>
       </c>
-      <c r="U24" s="2">
+      <c r="X24" s="3">
+        <v>929000</v>
+      </c>
+      <c r="Y24" s="2">
         <v>46168</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>99635</v>
       </c>
-      <c r="W24" s="3">
+      <c r="AA24" s="3">
         <v>63198436913</v>
       </c>
-      <c r="X24" s="3">
+      <c r="AB24" s="3">
         <v>99862.720000000001</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AC24" s="3">
         <v>0.01</v>
       </c>
-      <c r="Z24" s="2">
-        <v>46168</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>106870</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1288273331779</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>107222.97</v>
-      </c>
       <c r="AD24" s="3">
-        <v>-0.02</v>
+        <v>634000</v>
       </c>
       <c r="AE24" s="2">
         <v>46168</v>
       </c>
       <c r="AF24" s="3">
+        <v>106870</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>1288273331779</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>107222.97</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>-0.02</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>12050000</v>
+      </c>
+      <c r="AK24" s="2">
+        <v>46168</v>
+      </c>
+      <c r="AL24" s="3">
         <v>53890</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AM24" s="3">
         <v>1181626412050</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AN24" s="3">
         <v>53886.31</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AO24" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ24" s="2">
+      <c r="AP24" s="3">
+        <v>21930000</v>
+      </c>
+      <c r="AQ24" s="2">
         <v>46168</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AR24" s="3">
         <v>51025</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AS24" s="3">
         <v>419408695995</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AT24" s="3">
         <v>51058.57</v>
       </c>
-      <c r="AN24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="2">
+      <c r="AU24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV24" s="3">
+        <v>8220000</v>
+      </c>
+      <c r="AW24" s="2">
         <v>46168</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AX24" s="3">
         <v>103620</v>
       </c>
-      <c r="AQ24" s="3">
+      <c r="AY24" s="3">
         <v>2103775671801</v>
       </c>
-      <c r="AR24" s="3">
+      <c r="AZ24" s="3">
         <v>103912.2</v>
       </c>
-      <c r="AS24" s="3">
+      <c r="BA24" s="3">
         <v>0.01</v>
       </c>
-      <c r="AT24" s="2">
+      <c r="BB24" s="3">
+        <v>20303000</v>
+      </c>
+      <c r="BC24" s="2">
         <v>46168</v>
       </c>
-      <c r="AU24" s="3">
+      <c r="BD24" s="3">
         <v>49935</v>
       </c>
-      <c r="AV24" s="3">
+      <c r="BE24" s="3">
         <v>35062518557</v>
       </c>
-      <c r="AW24" s="3">
+      <c r="BF24" s="3">
         <v>50019.6</v>
       </c>
-      <c r="AX24" s="3">
+      <c r="BG24" s="3">
         <v>0.01</v>
       </c>
-      <c r="AY24" s="2">
+      <c r="BH24" s="3">
+        <v>702000</v>
+      </c>
+      <c r="BI24" s="2">
         <v>46168</v>
       </c>
-      <c r="AZ24" s="3">
+      <c r="BJ24" s="3">
         <v>114690</v>
       </c>
-      <c r="BA24" s="3">
+      <c r="BK24" s="3">
         <v>585437303892</v>
       </c>
-      <c r="BB24" s="3">
+      <c r="BL24" s="3">
         <v>114935.12</v>
       </c>
-      <c r="BC24" s="3">
+      <c r="BM24" s="3">
         <v>0.01</v>
       </c>
+      <c r="BN24" s="3">
+        <v>5102000</v>
+      </c>
     </row>
-    <row r="25" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>46164</v>
       </c>
@@ -33903,158 +34650,191 @@
       <c r="E25" s="3">
         <v>0.04</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
+        <v>38851000</v>
+      </c>
+      <c r="G25" s="2">
         <v>46164</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>88600</v>
       </c>
-      <c r="H25" s="3">
+      <c r="I25" s="3">
         <v>288634499989</v>
       </c>
-      <c r="I25" s="3">
+      <c r="J25" s="3">
         <v>88637.05</v>
       </c>
-      <c r="J25" s="3">
+      <c r="K25" s="3">
         <v>-0.1</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="M25" s="2">
         <v>46164</v>
       </c>
-      <c r="L25" s="3">
+      <c r="N25" s="3">
         <v>93385</v>
       </c>
-      <c r="M25" s="3">
+      <c r="O25" s="3">
         <v>341414628243</v>
       </c>
-      <c r="N25" s="3">
+      <c r="P25" s="3">
         <v>93340.86</v>
       </c>
-      <c r="O25" s="3">
+      <c r="Q25" s="3">
         <v>0.16</v>
       </c>
-      <c r="P25" s="2">
+      <c r="R25" s="3">
+        <v>3679000</v>
+      </c>
+      <c r="S25" s="2">
         <v>46164</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="T25" s="3">
         <v>98290</v>
       </c>
-      <c r="R25" s="3">
+      <c r="U25" s="3">
         <v>91116272472</v>
       </c>
-      <c r="S25" s="3">
+      <c r="V25" s="3">
         <v>98560.48</v>
       </c>
-      <c r="T25" s="3">
+      <c r="W25" s="3">
         <v>-0.05</v>
       </c>
-      <c r="U25" s="2">
+      <c r="X25" s="3">
+        <v>929000</v>
+      </c>
+      <c r="Y25" s="2">
         <v>46164</v>
       </c>
-      <c r="V25" s="3">
+      <c r="Z25" s="3">
         <v>99580</v>
       </c>
-      <c r="W25" s="3">
+      <c r="AA25" s="3">
         <v>63108895012</v>
       </c>
-      <c r="X25" s="3">
+      <c r="AB25" s="3">
         <v>99682.08</v>
       </c>
-      <c r="Y25" s="3">
+      <c r="AC25" s="3">
         <v>-0.05</v>
       </c>
-      <c r="Z25" s="2">
-        <v>46164</v>
-      </c>
-      <c r="AA25" s="3">
-        <v>106830</v>
-      </c>
-      <c r="AB25" s="3">
-        <v>1287850495218</v>
-      </c>
-      <c r="AC25" s="3">
-        <v>106910.65</v>
-      </c>
       <c r="AD25" s="3">
-        <v>-0.04</v>
+        <v>634000</v>
       </c>
       <c r="AE25" s="2">
         <v>46164</v>
       </c>
       <c r="AF25" s="3">
+        <v>106830</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>1287850495218</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>106910.65</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>-0.04</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>12074000</v>
+      </c>
+      <c r="AK25" s="2">
+        <v>46164</v>
+      </c>
+      <c r="AL25" s="3">
         <v>53880</v>
       </c>
-      <c r="AG25" s="3">
+      <c r="AM25" s="3">
         <v>1181238918964</v>
       </c>
-      <c r="AH25" s="3">
+      <c r="AN25" s="3">
         <v>53881.73</v>
       </c>
-      <c r="AI25" s="3">
+      <c r="AO25" s="3">
         <v>0.02</v>
       </c>
-      <c r="AJ25" s="2">
+      <c r="AP25" s="3">
+        <v>21930000</v>
+      </c>
+      <c r="AQ25" s="2">
         <v>46164</v>
       </c>
-      <c r="AK25" s="3">
+      <c r="AR25" s="3">
         <v>51015</v>
       </c>
-      <c r="AL25" s="3">
+      <c r="AS25" s="3">
         <v>419418575045</v>
       </c>
-      <c r="AM25" s="3">
+      <c r="AT25" s="3">
         <v>51022.96</v>
       </c>
-      <c r="AN25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="2">
+      <c r="AU25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV25" s="3">
+        <v>8226000</v>
+      </c>
+      <c r="AW25" s="2">
         <v>46164</v>
       </c>
-      <c r="AP25" s="3">
+      <c r="AX25" s="3">
         <v>103520</v>
       </c>
-      <c r="AQ25" s="3">
+      <c r="AY25" s="3">
         <v>2099143188911</v>
       </c>
-      <c r="AR25" s="3">
+      <c r="AZ25" s="3">
         <v>103618.96</v>
       </c>
-      <c r="AS25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT25" s="2">
+      <c r="BA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="BB25" s="3">
+        <v>20304000</v>
+      </c>
+      <c r="BC25" s="2">
         <v>46164</v>
       </c>
-      <c r="AU25" s="3">
+      <c r="BD25" s="3">
         <v>49930</v>
       </c>
-      <c r="AV25" s="3">
+      <c r="BE25" s="3">
         <v>35021121671</v>
       </c>
-      <c r="AW25" s="3">
+      <c r="BF25" s="3">
         <v>49946.61</v>
       </c>
-      <c r="AX25" s="3">
+      <c r="BG25" s="3">
         <v>-0.02</v>
       </c>
-      <c r="AY25" s="2">
+      <c r="BH25" s="3">
+        <v>702000</v>
+      </c>
+      <c r="BI25" s="2">
         <v>46164</v>
       </c>
-      <c r="AZ25" s="3">
+      <c r="BJ25" s="3">
         <v>114680</v>
       </c>
-      <c r="BA25" s="3">
+      <c r="BK25" s="3">
         <v>587248877434</v>
       </c>
-      <c r="BB25" s="3">
+      <c r="BL25" s="3">
         <v>114746.63</v>
       </c>
-      <c r="BC25" s="3">
+      <c r="BM25" s="3">
         <v>-0.05</v>
       </c>
+      <c r="BN25" s="3">
+        <v>5124000</v>
+      </c>
     </row>
-    <row r="26" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>46163</v>
       </c>
@@ -34070,158 +34850,191 @@
       <c r="E26" s="3">
         <v>0.17</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
+        <v>39005000</v>
+      </c>
+      <c r="G26" s="2">
         <v>46163</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>88120</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>288566024023</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>88240.45</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>0.41</v>
       </c>
-      <c r="K26" s="2">
+      <c r="L26" s="3">
+        <v>3271000</v>
+      </c>
+      <c r="M26" s="2">
         <v>46163</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>92810</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>341417807397</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>92800.93</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>0.63</v>
       </c>
-      <c r="P26" s="2">
+      <c r="R26" s="3">
+        <v>3679000</v>
+      </c>
+      <c r="S26" s="2">
         <v>46163</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>97950</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>91020658086</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>98079.95</v>
       </c>
-      <c r="T26" s="3">
+      <c r="W26" s="3">
         <v>0.21</v>
       </c>
-      <c r="U26" s="2">
+      <c r="X26" s="3">
+        <v>929000</v>
+      </c>
+      <c r="Y26" s="2">
         <v>46163</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>99530</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>63097869045</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>99540.84</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>0.04</v>
       </c>
-      <c r="Z26" s="2">
-        <v>46163</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>106685</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>1292120778159</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>106663.12</v>
-      </c>
       <c r="AD26" s="3">
-        <v>0.16</v>
+        <v>634000</v>
       </c>
       <c r="AE26" s="2">
         <v>46163</v>
       </c>
       <c r="AF26" s="3">
+        <v>106685</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>1292120778159</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>106663.12</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>12117000</v>
+      </c>
+      <c r="AK26" s="2">
+        <v>46163</v>
+      </c>
+      <c r="AL26" s="3">
         <v>53870</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AM26" s="3">
         <v>1179761380514</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AN26" s="3">
         <v>53864.06</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AO26" s="3">
         <v>0.03</v>
       </c>
-      <c r="AJ26" s="2">
+      <c r="AP26" s="3">
+        <v>21904000</v>
+      </c>
+      <c r="AQ26" s="2">
         <v>46163</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AR26" s="3">
         <v>50990</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AS26" s="3">
         <v>404902784903</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AT26" s="3">
         <v>50986.94</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AU26" s="3">
         <v>0.06</v>
       </c>
-      <c r="AO26" s="2">
+      <c r="AV26" s="3">
+        <v>7942000</v>
+      </c>
+      <c r="AW26" s="2">
         <v>46163</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AX26" s="3">
         <v>103385</v>
       </c>
-      <c r="AQ26" s="3">
+      <c r="AY26" s="3">
         <v>2106437859171</v>
       </c>
-      <c r="AR26" s="3">
+      <c r="AZ26" s="3">
         <v>103385.7</v>
       </c>
-      <c r="AS26" s="3">
+      <c r="BA26" s="3">
         <v>0.13</v>
       </c>
-      <c r="AT26" s="2">
+      <c r="BB26" s="3">
+        <v>20378000</v>
+      </c>
+      <c r="BC26" s="2">
         <v>46163</v>
       </c>
-      <c r="AU26" s="3">
+      <c r="BD26" s="3">
         <v>49895</v>
       </c>
-      <c r="AV26" s="3">
+      <c r="BE26" s="3">
         <v>35016791400</v>
       </c>
-      <c r="AW26" s="3">
+      <c r="BF26" s="3">
         <v>49887.64</v>
       </c>
-      <c r="AX26" s="3">
+      <c r="BG26" s="3">
         <v>0.08</v>
       </c>
-      <c r="AY26" s="2">
+      <c r="BH26" s="3">
+        <v>702000</v>
+      </c>
+      <c r="BI26" s="2">
         <v>46163</v>
       </c>
-      <c r="AZ26" s="3">
+      <c r="BJ26" s="3">
         <v>114635</v>
       </c>
-      <c r="BA26" s="3">
+      <c r="BK26" s="3">
         <v>587294382652</v>
       </c>
-      <c r="BB26" s="3">
+      <c r="BL26" s="3">
         <v>114607.51</v>
       </c>
-      <c r="BC26" s="3">
+      <c r="BM26" s="3">
         <v>0.06</v>
       </c>
+      <c r="BN26" s="3">
+        <v>5124000</v>
+      </c>
     </row>
-    <row r="27" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>46162</v>
       </c>
@@ -34237,158 +35050,191 @@
       <c r="E27" s="3">
         <v>0</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
+        <v>39074000</v>
+      </c>
+      <c r="G27" s="2">
         <v>46162</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>87810</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>288662364824</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>88219.51</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-0.11</v>
       </c>
-      <c r="K27" s="2">
+      <c r="L27" s="3">
+        <v>3276000</v>
+      </c>
+      <c r="M27" s="2">
         <v>46162</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>92165</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>339458358003</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>92801.8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>0.01</v>
       </c>
-      <c r="P27" s="2">
+      <c r="R27" s="3">
+        <v>3670000</v>
+      </c>
+      <c r="S27" s="2">
         <v>46162</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
         <v>97645</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>90836274620</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>97977.03</v>
       </c>
-      <c r="T27" s="3">
+      <c r="W27" s="3">
         <v>-0.03</v>
       </c>
-      <c r="U27" s="2">
+      <c r="X27" s="3">
+        <v>928000</v>
+      </c>
+      <c r="Y27" s="2">
         <v>46162</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>99485</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>60124384055</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>99523.45</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>0.01</v>
       </c>
-      <c r="Z27" s="2">
-        <v>46162</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>106560</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>1291616959938</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>106637.02</v>
-      </c>
       <c r="AD27" s="3">
-        <v>0.04</v>
+        <v>604000</v>
       </c>
       <c r="AE27" s="2">
         <v>46162</v>
       </c>
       <c r="AF27" s="3">
+        <v>106560</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>1291616959938</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>106637.02</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>12118000</v>
+      </c>
+      <c r="AK27" s="2">
+        <v>46162</v>
+      </c>
+      <c r="AL27" s="3">
         <v>53870</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AM27" s="3">
         <v>1179677581158</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AN27" s="3">
         <v>53860.55</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AO27" s="3">
         <v>0.02</v>
       </c>
-      <c r="AJ27" s="2">
+      <c r="AP27" s="3">
+        <v>21904000</v>
+      </c>
+      <c r="AQ27" s="2">
         <v>46162</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AR27" s="3">
         <v>50995</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AS27" s="3">
         <v>389922706051</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AT27" s="3">
         <v>50982.47</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AU27" s="3">
         <v>0.01</v>
       </c>
-      <c r="AO27" s="2">
+      <c r="AV27" s="3">
+        <v>7648000</v>
+      </c>
+      <c r="AW27" s="2">
         <v>46162</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AX27" s="3">
         <v>103240</v>
       </c>
-      <c r="AQ27" s="3">
+      <c r="AY27" s="3">
         <v>2106872779256</v>
       </c>
-      <c r="AR27" s="3">
+      <c r="AZ27" s="3">
         <v>103368.23</v>
       </c>
-      <c r="AS27" s="3">
+      <c r="BA27" s="3">
         <v>0.02</v>
       </c>
-      <c r="AT27" s="2">
+      <c r="BB27" s="3">
+        <v>20392000</v>
+      </c>
+      <c r="BC27" s="2">
         <v>46162</v>
       </c>
-      <c r="AU27" s="3">
+      <c r="BD27" s="3">
         <v>49895</v>
       </c>
-      <c r="AV27" s="3">
+      <c r="BE27" s="3">
         <v>35020956076</v>
       </c>
-      <c r="AW27" s="3">
+      <c r="BF27" s="3">
         <v>49881.47</v>
       </c>
-      <c r="AX27" s="3">
+      <c r="BG27" s="3">
         <v>0.03</v>
       </c>
-      <c r="AY27" s="2">
+      <c r="BH27" s="3">
+        <v>702000</v>
+      </c>
+      <c r="BI27" s="2">
         <v>46162</v>
       </c>
-      <c r="AZ27" s="3">
+      <c r="BJ27" s="3">
         <v>114670</v>
       </c>
-      <c r="BA27" s="3">
+      <c r="BK27" s="3">
         <v>589798840362</v>
       </c>
-      <c r="BB27" s="3">
+      <c r="BL27" s="3">
         <v>114616.39</v>
       </c>
-      <c r="BC27" s="3">
+      <c r="BM27" s="3">
         <v>0.02</v>
       </c>
+      <c r="BN27" s="3">
+        <v>5144000</v>
+      </c>
     </row>
-    <row r="28" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>46161</v>
       </c>
@@ -34404,158 +35250,191 @@
       <c r="E28" s="3">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
+        <v>38614000</v>
+      </c>
+      <c r="G28" s="2">
         <v>46161</v>
       </c>
-      <c r="G28" s="3">
+      <c r="H28" s="3">
         <v>87965</v>
       </c>
-      <c r="H28" s="3">
+      <c r="I28" s="3">
         <v>288286951071</v>
       </c>
-      <c r="I28" s="3">
+      <c r="J28" s="3">
         <v>88114.27</v>
       </c>
-      <c r="J28" s="3">
+      <c r="K28" s="3">
         <v>-0.35</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="3">
+        <v>3276000</v>
+      </c>
+      <c r="M28" s="2">
         <v>46161</v>
       </c>
-      <c r="L28" s="3">
+      <c r="N28" s="3">
         <v>92440</v>
       </c>
-      <c r="M28" s="3">
+      <c r="O28" s="3">
         <v>339657504006</v>
       </c>
-      <c r="N28" s="3">
+      <c r="P28" s="3">
         <v>92495.47</v>
       </c>
-      <c r="O28" s="3">
+      <c r="Q28" s="3">
         <v>-0.36</v>
       </c>
-      <c r="P28" s="2">
+      <c r="R28" s="3">
+        <v>3678000</v>
+      </c>
+      <c r="S28" s="2">
         <v>46161</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="T28" s="3">
         <v>97785</v>
       </c>
-      <c r="R28" s="3">
+      <c r="U28" s="3">
         <v>109115943200</v>
       </c>
-      <c r="S28" s="3">
+      <c r="V28" s="3">
         <v>97883.92</v>
       </c>
-      <c r="T28" s="3">
+      <c r="W28" s="3">
         <v>-0.24</v>
       </c>
-      <c r="U28" s="2">
+      <c r="X28" s="3">
+        <v>1118000</v>
+      </c>
+      <c r="Y28" s="2">
         <v>46161</v>
       </c>
-      <c r="V28" s="3">
+      <c r="Z28" s="3">
         <v>99530</v>
       </c>
-      <c r="W28" s="3">
+      <c r="AA28" s="3">
         <v>58107195607</v>
       </c>
-      <c r="X28" s="3">
+      <c r="AB28" s="3">
         <v>99543.679999999993</v>
       </c>
-      <c r="Y28" s="3">
+      <c r="AC28" s="3">
         <v>-0.06</v>
       </c>
-      <c r="Z28" s="2">
-        <v>46161</v>
-      </c>
-      <c r="AA28" s="3">
-        <v>106625</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>1299946807030</v>
-      </c>
-      <c r="AC28" s="3">
-        <v>106586.64</v>
-      </c>
       <c r="AD28" s="3">
-        <v>-0.02</v>
+        <v>584000</v>
       </c>
       <c r="AE28" s="2">
         <v>46161</v>
       </c>
       <c r="AF28" s="3">
+        <v>106625</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>1299946807030</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>106586.64</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>-0.02</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>12204000</v>
+      </c>
+      <c r="AK28" s="2">
+        <v>46161</v>
+      </c>
+      <c r="AL28" s="3">
         <v>53870</v>
       </c>
-      <c r="AG28" s="3">
+      <c r="AM28" s="3">
         <v>1179476619215</v>
       </c>
-      <c r="AH28" s="3">
+      <c r="AN28" s="3">
         <v>53856.72</v>
       </c>
-      <c r="AI28" s="3">
+      <c r="AO28" s="3">
         <v>0.02</v>
       </c>
-      <c r="AJ28" s="2">
+      <c r="AP28" s="3">
+        <v>21902000</v>
+      </c>
+      <c r="AQ28" s="2">
         <v>46161</v>
       </c>
-      <c r="AK28" s="3">
+      <c r="AR28" s="3">
         <v>50970</v>
       </c>
-      <c r="AL28" s="3">
+      <c r="AS28" s="3">
         <v>391847511054</v>
       </c>
-      <c r="AM28" s="3">
+      <c r="AT28" s="3">
         <v>50983.62</v>
       </c>
-      <c r="AN28" s="3">
+      <c r="AU28" s="3">
         <v>0.02</v>
       </c>
-      <c r="AO28" s="2">
+      <c r="AV28" s="3">
+        <v>7686000</v>
+      </c>
+      <c r="AW28" s="2">
         <v>46161</v>
       </c>
-      <c r="AP28" s="3">
+      <c r="AX28" s="3">
         <v>103360</v>
       </c>
-      <c r="AQ28" s="3">
+      <c r="AY28" s="3">
         <v>2118640735892</v>
       </c>
-      <c r="AR28" s="3">
+      <c r="AZ28" s="3">
         <v>103318.59</v>
       </c>
-      <c r="AS28" s="3">
+      <c r="BA28" s="3">
         <v>-0.08</v>
       </c>
-      <c r="AT28" s="2">
+      <c r="BB28" s="3">
+        <v>20519000</v>
+      </c>
+      <c r="BC28" s="2">
         <v>46161</v>
       </c>
-      <c r="AU28" s="3">
+      <c r="BD28" s="3">
         <v>49855</v>
       </c>
-      <c r="AV28" s="3">
+      <c r="BE28" s="3">
         <v>34909837183</v>
       </c>
-      <c r="AW28" s="3">
+      <c r="BF28" s="3">
         <v>49887.4</v>
       </c>
-      <c r="AX28" s="3">
+      <c r="BG28" s="3">
         <v>0.02</v>
       </c>
-      <c r="AY28" s="2">
+      <c r="BH28" s="3">
+        <v>700000</v>
+      </c>
+      <c r="BI28" s="2">
         <v>46161</v>
       </c>
-      <c r="AZ28" s="3">
+      <c r="BJ28" s="3">
         <v>114600</v>
       </c>
-      <c r="BA28" s="3">
+      <c r="BK28" s="3">
         <v>590727083847</v>
       </c>
-      <c r="BB28" s="3">
+      <c r="BL28" s="3">
         <v>114657.63</v>
       </c>
-      <c r="BC28" s="3">
+      <c r="BM28" s="3">
         <v>0.01</v>
       </c>
+      <c r="BN28" s="3">
+        <v>5154000</v>
+      </c>
     </row>
-    <row r="29" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>46160</v>
       </c>
@@ -34571,158 +35450,191 @@
       <c r="E29" s="3">
         <v>-0.01</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
+        <v>38481000</v>
+      </c>
+      <c r="G29" s="2">
         <v>46160</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>88415</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>289759952626</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>87999.679999999993</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-0.04</v>
       </c>
-      <c r="K29" s="2">
+      <c r="L29" s="3">
+        <v>3277000</v>
+      </c>
+      <c r="M29" s="2">
         <v>46160</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>93345</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>337868788667</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>92348.42</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>0.1</v>
       </c>
-      <c r="P29" s="2">
+      <c r="R29" s="3">
+        <v>3617000</v>
+      </c>
+      <c r="S29" s="2">
         <v>46160</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="T29" s="3">
         <v>97745</v>
       </c>
-      <c r="R29" s="3">
+      <c r="U29" s="3">
         <v>112049657234</v>
       </c>
-      <c r="S29" s="3">
+      <c r="V29" s="3">
         <v>97599.23</v>
       </c>
-      <c r="T29" s="3">
+      <c r="W29" s="3">
         <v>0.19</v>
       </c>
-      <c r="U29" s="2">
+      <c r="X29" s="3">
+        <v>1146000</v>
+      </c>
+      <c r="Y29" s="2">
         <v>46160</v>
       </c>
-      <c r="V29" s="3">
+      <c r="Z29" s="3">
         <v>99400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="AA29" s="3">
         <v>56098319440</v>
       </c>
-      <c r="X29" s="3">
+      <c r="AB29" s="3">
         <v>99498.62</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AC29" s="3">
         <v>0.03</v>
       </c>
-      <c r="Z29" s="2">
-        <v>46160</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>106745</v>
-      </c>
-      <c r="AB29" s="3">
-        <v>1306344317200</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>106518.09</v>
-      </c>
       <c r="AD29" s="3">
-        <v>0.1</v>
+        <v>564000</v>
       </c>
       <c r="AE29" s="2">
         <v>46160</v>
       </c>
       <c r="AF29" s="3">
+        <v>106745</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>1306344317200</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>106518.09</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>12241000</v>
+      </c>
+      <c r="AK29" s="2">
+        <v>46160</v>
+      </c>
+      <c r="AL29" s="3">
         <v>53855</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AM29" s="3">
         <v>1179583767066</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AN29" s="3">
         <v>53852.46</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AO29" s="3">
         <v>0.03</v>
       </c>
-      <c r="AJ29" s="2">
+      <c r="AP29" s="3">
+        <v>21906000</v>
+      </c>
+      <c r="AQ29" s="2">
         <v>46160</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AR29" s="3">
         <v>50985</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AS29" s="3">
         <v>393386066078</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AT29" s="3">
         <v>50981.98</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AU29" s="3">
         <v>-0.02</v>
       </c>
-      <c r="AO29" s="2">
+      <c r="AV29" s="3">
+        <v>7718000</v>
+      </c>
+      <c r="AW29" s="2">
         <v>46160</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AX29" s="3">
         <v>103390</v>
       </c>
-      <c r="AQ29" s="3">
+      <c r="AY29" s="3">
         <v>2123478952058</v>
       </c>
-      <c r="AR29" s="3">
+      <c r="AZ29" s="3">
         <v>103252.63</v>
       </c>
-      <c r="AS29" s="3">
+      <c r="BA29" s="3">
         <v>0.1</v>
       </c>
-      <c r="AT29" s="2">
+      <c r="BB29" s="3">
+        <v>20526000</v>
+      </c>
+      <c r="BC29" s="2">
         <v>46160</v>
       </c>
-      <c r="AU29" s="3">
+      <c r="BD29" s="3">
         <v>49875</v>
       </c>
-      <c r="AV29" s="3">
+      <c r="BE29" s="3">
         <v>34998144193</v>
       </c>
-      <c r="AW29" s="3">
+      <c r="BF29" s="3">
         <v>49871.199999999997</v>
       </c>
-      <c r="AX29" s="3">
+      <c r="BG29" s="3">
         <v>-0.03</v>
       </c>
-      <c r="AY29" s="2">
+      <c r="BH29" s="3">
+        <v>702000</v>
+      </c>
+      <c r="BI29" s="2">
         <v>46160</v>
       </c>
-      <c r="AZ29" s="3">
+      <c r="BJ29" s="3">
         <v>114465</v>
       </c>
-      <c r="BA29" s="3">
+      <c r="BK29" s="3">
         <v>593872518240</v>
       </c>
-      <c r="BB29" s="3">
+      <c r="BL29" s="3">
         <v>114615.27</v>
       </c>
-      <c r="BC29" s="3">
+      <c r="BM29" s="3">
         <v>-0.01</v>
       </c>
+      <c r="BN29" s="3">
+        <v>5184000</v>
+      </c>
     </row>
-    <row r="30" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>46157</v>
       </c>
@@ -34738,158 +35650,191 @@
       <c r="E30" s="3">
         <v>0</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
+        <v>38039000</v>
+      </c>
+      <c r="G30" s="2">
         <v>46157</v>
       </c>
-      <c r="G30" s="3">
+      <c r="H30" s="3">
         <v>89730</v>
       </c>
-      <c r="H30" s="3">
+      <c r="I30" s="3">
         <v>293861433517</v>
       </c>
-      <c r="I30" s="3">
+      <c r="J30" s="3">
         <v>88422.32</v>
       </c>
-      <c r="J30" s="3">
+      <c r="K30" s="3">
         <v>-0.01</v>
       </c>
-      <c r="K30" s="2">
+      <c r="L30" s="3">
+        <v>3277000</v>
+      </c>
+      <c r="M30" s="2">
         <v>46157</v>
       </c>
-      <c r="L30" s="3">
+      <c r="N30" s="3">
         <v>95805</v>
       </c>
-      <c r="M30" s="3">
+      <c r="O30" s="3">
         <v>348097229405</v>
       </c>
-      <c r="N30" s="3">
+      <c r="P30" s="3">
         <v>93411.33</v>
       </c>
-      <c r="O30" s="3">
+      <c r="Q30" s="3">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="P30" s="2">
+      <c r="R30" s="3">
+        <v>3637000</v>
+      </c>
+      <c r="S30" s="2">
         <v>46157</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="T30" s="3">
         <v>98880</v>
       </c>
-      <c r="R30" s="3">
+      <c r="U30" s="3">
         <v>113061817822</v>
       </c>
-      <c r="S30" s="3">
+      <c r="V30" s="3">
         <v>97774.57</v>
       </c>
-      <c r="T30" s="3">
+      <c r="W30" s="3">
         <v>-0.03</v>
       </c>
-      <c r="U30" s="2">
+      <c r="X30" s="3">
+        <v>1145000</v>
+      </c>
+      <c r="Y30" s="2">
         <v>46157</v>
       </c>
-      <c r="V30" s="3">
+      <c r="Z30" s="3">
         <v>99725</v>
       </c>
-      <c r="W30" s="3">
+      <c r="AA30" s="3">
         <v>55260097937</v>
       </c>
-      <c r="X30" s="3">
+      <c r="AB30" s="3">
         <v>99465.11</v>
       </c>
-      <c r="Y30" s="3">
+      <c r="AC30" s="3">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="Z30" s="2">
-        <v>46157</v>
-      </c>
-      <c r="AA30" s="3">
-        <v>107555</v>
-      </c>
-      <c r="AB30" s="3">
-        <v>1291192061654</v>
-      </c>
-      <c r="AC30" s="3">
-        <v>106718.76</v>
-      </c>
       <c r="AD30" s="3">
-        <v>0.02</v>
+        <v>554000</v>
       </c>
       <c r="AE30" s="2">
         <v>46157</v>
       </c>
       <c r="AF30" s="3">
+        <v>107555</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>1291192061654</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>106718.76</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>12020000</v>
+      </c>
+      <c r="AK30" s="2">
+        <v>46157</v>
+      </c>
+      <c r="AL30" s="3">
         <v>53845</v>
       </c>
-      <c r="AG30" s="3">
+      <c r="AM30" s="3">
         <v>1192250882062</v>
       </c>
-      <c r="AH30" s="3">
+      <c r="AN30" s="3">
         <v>53847.519999999997</v>
       </c>
-      <c r="AI30" s="3">
+      <c r="AO30" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ30" s="2">
+      <c r="AP30" s="3">
+        <v>22146000</v>
+      </c>
+      <c r="AQ30" s="2">
         <v>46157</v>
       </c>
-      <c r="AK30" s="3">
+      <c r="AR30" s="3">
         <v>51035</v>
       </c>
-      <c r="AL30" s="3">
+      <c r="AS30" s="3">
         <v>393483778198</v>
       </c>
-      <c r="AM30" s="3">
+      <c r="AT30" s="3">
         <v>50969.95</v>
       </c>
-      <c r="AN30" s="3">
+      <c r="AU30" s="3">
         <v>0.03</v>
       </c>
-      <c r="AO30" s="2">
+      <c r="AV30" s="3">
+        <v>7714000</v>
+      </c>
+      <c r="AW30" s="2">
         <v>46157</v>
       </c>
-      <c r="AP30" s="3">
+      <c r="AX30" s="3">
         <v>104210</v>
       </c>
-      <c r="AQ30" s="3">
+      <c r="AY30" s="3">
         <v>2135104272676</v>
       </c>
-      <c r="AR30" s="3">
+      <c r="AZ30" s="3">
         <v>103453.13</v>
       </c>
-      <c r="AS30" s="3">
+      <c r="BA30" s="3">
         <v>-0.06</v>
       </c>
-      <c r="AT30" s="2">
+      <c r="BB30" s="3">
+        <v>20501000</v>
+      </c>
+      <c r="BC30" s="2">
         <v>46157</v>
       </c>
-      <c r="AU30" s="3">
+      <c r="BD30" s="3">
         <v>49995</v>
       </c>
-      <c r="AV30" s="3">
+      <c r="BE30" s="3">
         <v>35074806010</v>
       </c>
-      <c r="AW30" s="3">
+      <c r="BF30" s="3">
         <v>49854.91</v>
       </c>
-      <c r="AX30" s="3">
+      <c r="BG30" s="3">
         <v>0.04</v>
       </c>
-      <c r="AY30" s="2">
+      <c r="BH30" s="3">
+        <v>702000</v>
+      </c>
+      <c r="BI30" s="2">
         <v>46157</v>
       </c>
-      <c r="AZ30" s="3">
+      <c r="BJ30" s="3">
         <v>114870</v>
       </c>
-      <c r="BA30" s="3">
+      <c r="BK30" s="3">
         <v>599266144333</v>
       </c>
-      <c r="BB30" s="3">
+      <c r="BL30" s="3">
         <v>114558.74</v>
       </c>
-      <c r="BC30" s="3">
+      <c r="BM30" s="3">
         <v>-0.08</v>
       </c>
+      <c r="BN30" s="3">
+        <v>5217000</v>
+      </c>
     </row>
-    <row r="31" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>46156</v>
       </c>
@@ -34905,158 +35850,191 @@
       <c r="E31" s="3">
         <v>0.11</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
+        <v>37990000</v>
+      </c>
+      <c r="G31" s="2">
         <v>46156</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>89995</v>
       </c>
-      <c r="H31" s="3">
+      <c r="I31" s="3">
         <v>303812109032</v>
       </c>
-      <c r="I31" s="3">
+      <c r="J31" s="3">
         <v>89673.919999999998</v>
       </c>
-      <c r="J31" s="3">
+      <c r="K31" s="3">
         <v>0.06</v>
       </c>
-      <c r="K31" s="2">
+      <c r="L31" s="3">
+        <v>3377000</v>
+      </c>
+      <c r="M31" s="2">
         <v>46156</v>
       </c>
-      <c r="L31" s="3">
+      <c r="N31" s="3">
         <v>96320</v>
       </c>
-      <c r="M31" s="3">
+      <c r="O31" s="3">
         <v>350290807012</v>
       </c>
-      <c r="N31" s="3">
+      <c r="P31" s="3">
         <v>95709.99</v>
       </c>
-      <c r="O31" s="3">
+      <c r="Q31" s="3">
         <v>0.1</v>
       </c>
-      <c r="P31" s="2">
+      <c r="R31" s="3">
+        <v>3637000</v>
+      </c>
+      <c r="S31" s="2">
         <v>46156</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="T31" s="3">
         <v>99050</v>
       </c>
-      <c r="R31" s="3">
+      <c r="U31" s="3">
         <v>113333731102</v>
       </c>
-      <c r="S31" s="3">
+      <c r="V31" s="3">
         <v>98743.95</v>
       </c>
-      <c r="T31" s="3">
+      <c r="W31" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="U31" s="2">
+      <c r="X31" s="3">
+        <v>1145000</v>
+      </c>
+      <c r="Y31" s="2">
         <v>46156</v>
       </c>
-      <c r="V31" s="3">
+      <c r="Z31" s="3">
         <v>99800</v>
       </c>
-      <c r="W31" s="3">
+      <c r="AA31" s="3">
         <v>55285461297</v>
       </c>
-      <c r="X31" s="3">
+      <c r="AB31" s="3">
         <v>99747.47</v>
       </c>
-      <c r="Y31" s="3">
+      <c r="AC31" s="3">
         <v>-0.02</v>
       </c>
-      <c r="Z31" s="2">
-        <v>46156</v>
-      </c>
-      <c r="AA31" s="3">
-        <v>107570</v>
-      </c>
-      <c r="AB31" s="3">
-        <v>1276244938526</v>
-      </c>
-      <c r="AC31" s="3">
-        <v>107420.3</v>
-      </c>
       <c r="AD31" s="3">
-        <v>0.13</v>
+        <v>554000</v>
       </c>
       <c r="AE31" s="2">
         <v>46156</v>
       </c>
       <c r="AF31" s="3">
+        <v>107570</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>1276244938526</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>107420.3</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>11864000</v>
+      </c>
+      <c r="AK31" s="2">
+        <v>46156</v>
+      </c>
+      <c r="AL31" s="3">
         <v>53840</v>
       </c>
-      <c r="AG31" s="3">
+      <c r="AM31" s="3">
         <v>1193331753698</v>
       </c>
-      <c r="AH31" s="3">
+      <c r="AN31" s="3">
         <v>53835.95</v>
       </c>
-      <c r="AI31" s="3">
+      <c r="AO31" s="3">
         <v>0.02</v>
       </c>
-      <c r="AJ31" s="2">
+      <c r="AP31" s="3">
+        <v>22168000</v>
+      </c>
+      <c r="AQ31" s="2">
         <v>46156</v>
       </c>
-      <c r="AK31" s="3">
+      <c r="AR31" s="3">
         <v>51010</v>
       </c>
-      <c r="AL31" s="3">
+      <c r="AS31" s="3">
         <v>392876388378</v>
       </c>
-      <c r="AM31" s="3">
+      <c r="AT31" s="3">
         <v>51009.05</v>
       </c>
-      <c r="AN31" s="3">
+      <c r="AU31" s="3">
         <v>0.05</v>
       </c>
-      <c r="AO31" s="2">
+      <c r="AV31" s="3">
+        <v>7702000</v>
+      </c>
+      <c r="AW31" s="2">
         <v>46156</v>
       </c>
-      <c r="AP31" s="3">
+      <c r="AX31" s="3">
         <v>104405</v>
       </c>
-      <c r="AQ31" s="3">
+      <c r="AY31" s="3">
         <v>2136317844227</v>
       </c>
-      <c r="AR31" s="3">
+      <c r="AZ31" s="3">
         <v>104146.35</v>
       </c>
-      <c r="AS31" s="3">
+      <c r="BA31" s="3">
         <v>0.06</v>
       </c>
-      <c r="AT31" s="2">
+      <c r="BB31" s="3">
+        <v>20482000</v>
+      </c>
+      <c r="BC31" s="2">
         <v>46156</v>
       </c>
-      <c r="AU31" s="3">
+      <c r="BD31" s="3">
         <v>49960</v>
       </c>
-      <c r="AV31" s="3">
+      <c r="BE31" s="3">
         <v>34585426145</v>
       </c>
-      <c r="AW31" s="3">
+      <c r="BF31" s="3">
         <v>49964.11</v>
       </c>
-      <c r="AX31" s="3">
+      <c r="BG31" s="3">
         <v>0.06</v>
       </c>
-      <c r="AY31" s="2">
+      <c r="BH31" s="3">
+        <v>692000</v>
+      </c>
+      <c r="BI31" s="2">
         <v>46156</v>
       </c>
-      <c r="AZ31" s="3">
+      <c r="BJ31" s="3">
         <v>114905</v>
       </c>
-      <c r="BA31" s="3">
+      <c r="BK31" s="3">
         <v>600643698815</v>
       </c>
-      <c r="BB31" s="3">
+      <c r="BL31" s="3">
         <v>114867.96</v>
       </c>
-      <c r="BC31" s="3">
-        <v>0</v>
+      <c r="BM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="BN31" s="3">
+        <v>5227000</v>
       </c>
     </row>
-    <row r="32" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>46155</v>
       </c>
@@ -35072,158 +36050,191 @@
       <c r="E32" s="3">
         <v>0.13</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
+        <v>37758000</v>
+      </c>
+      <c r="G32" s="2">
         <v>46155</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>89975</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>303101116905</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>89965.09</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>0.03</v>
       </c>
-      <c r="K32" s="2">
+      <c r="L32" s="3">
+        <v>3373000</v>
+      </c>
+      <c r="M32" s="2">
         <v>46155</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>96470</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>349568448154</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>96313.12</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>0.01</v>
       </c>
-      <c r="P32" s="2">
+      <c r="R32" s="3">
+        <v>3634000</v>
+      </c>
+      <c r="S32" s="2">
         <v>46155</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="T32" s="3">
         <v>98985</v>
       </c>
-      <c r="R32" s="3">
+      <c r="U32" s="3">
         <v>115408244436</v>
       </c>
-      <c r="S32" s="3">
+      <c r="V32" s="3">
         <v>98981.42</v>
       </c>
-      <c r="T32" s="3">
+      <c r="W32" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="U32" s="2">
+      <c r="X32" s="3">
+        <v>1167000</v>
+      </c>
+      <c r="Y32" s="2">
         <v>46155</v>
       </c>
-      <c r="V32" s="3">
+      <c r="Z32" s="3">
         <v>99770</v>
       </c>
-      <c r="W32" s="3">
+      <c r="AA32" s="3">
         <v>54335898322</v>
       </c>
-      <c r="X32" s="3">
+      <c r="AB32" s="3">
         <v>99793.25</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AC32" s="3">
         <v>0.01</v>
       </c>
-      <c r="Z32" s="2">
-        <v>46155</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>107550</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>1269344779740</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>107572.9</v>
-      </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>545000</v>
       </c>
       <c r="AE32" s="2">
         <v>46155</v>
       </c>
       <c r="AF32" s="3">
+        <v>107550</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>1269344779740</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>107572.9</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>11809000</v>
+      </c>
+      <c r="AK32" s="2">
+        <v>46155</v>
+      </c>
+      <c r="AL32" s="3">
         <v>53830</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AM32" s="3">
         <v>1190423594698</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AN32" s="3">
         <v>53831.28</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AO32" s="3">
         <v>0.02</v>
       </c>
-      <c r="AJ32" s="2">
+      <c r="AP32" s="3">
+        <v>22116000</v>
+      </c>
+      <c r="AQ32" s="2">
         <v>46155</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AR32" s="3">
         <v>51000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AS32" s="3">
         <v>389183198846</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AT32" s="3">
         <v>51009.66</v>
       </c>
-      <c r="AN32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="2">
+      <c r="AU32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="3">
+        <v>7634000</v>
+      </c>
+      <c r="AW32" s="2">
         <v>46155</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AX32" s="3">
         <v>104260</v>
       </c>
-      <c r="AQ32" s="3">
+      <c r="AY32" s="3">
         <v>2130320886472</v>
       </c>
-      <c r="AR32" s="3">
+      <c r="AZ32" s="3">
         <v>104302.21</v>
       </c>
-      <c r="AS32" s="3">
+      <c r="BA32" s="3">
         <v>0.1</v>
       </c>
-      <c r="AT32" s="2">
+      <c r="BB32" s="3">
+        <v>20442000</v>
+      </c>
+      <c r="BC32" s="2">
         <v>46155</v>
       </c>
-      <c r="AU32" s="3">
+      <c r="BD32" s="3">
         <v>49975</v>
       </c>
-      <c r="AV32" s="3">
+      <c r="BE32" s="3">
         <v>34356454578</v>
       </c>
-      <c r="AW32" s="3">
+      <c r="BF32" s="3">
         <v>49978.94</v>
       </c>
-      <c r="AX32" s="3">
+      <c r="BG32" s="3">
         <v>-0.04</v>
       </c>
-      <c r="AY32" s="2">
+      <c r="BH32" s="3">
+        <v>688000</v>
+      </c>
+      <c r="BI32" s="2">
         <v>46155</v>
       </c>
-      <c r="AZ32" s="3">
+      <c r="BJ32" s="3">
         <v>114820</v>
       </c>
-      <c r="BA32" s="3">
+      <c r="BK32" s="3">
         <v>603530575424</v>
       </c>
-      <c r="BB32" s="3">
+      <c r="BL32" s="3">
         <v>114911.75</v>
       </c>
-      <c r="BC32" s="3">
+      <c r="BM32" s="3">
         <v>-0.01</v>
       </c>
+      <c r="BN32" s="3">
+        <v>5257000</v>
+      </c>
     </row>
-    <row r="33" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:66" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>46154</v>
       </c>
@@ -35239,155 +36250,188 @@
       <c r="E33" s="3">
         <v>0.03</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
+        <v>37851000</v>
+      </c>
+      <c r="G33" s="2">
         <v>46154</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>91060</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>309833370369</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>89860.99</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>0.13</v>
       </c>
-      <c r="K33" s="2">
+      <c r="L33" s="3">
+        <v>3402000</v>
+      </c>
+      <c r="M33" s="2">
         <v>46154</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>98770</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>353373933291</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>96193.85</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="P33" s="2">
+      <c r="R33" s="3">
+        <v>3584000</v>
+      </c>
+      <c r="S33" s="2">
         <v>46154</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>99725</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>118626252579</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>98893.1</v>
       </c>
-      <c r="T33" s="3">
+      <c r="W33" s="3">
         <v>0.09</v>
       </c>
-      <c r="U33" s="2">
+      <c r="X33" s="3">
+        <v>1189000</v>
+      </c>
+      <c r="Y33" s="2">
         <v>46154</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>99890</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>54471440648</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>99698.9</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Z33" s="2">
-        <v>46154</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>108155</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>1280244609572</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>107489.61</v>
-      </c>
       <c r="AD33" s="3">
-        <v>0.06</v>
+        <v>545000</v>
       </c>
       <c r="AE33" s="2">
         <v>46154</v>
       </c>
       <c r="AF33" s="3">
+        <v>108155</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>1280244609572</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>107489.61</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>11837000</v>
+      </c>
+      <c r="AK33" s="2">
+        <v>46154</v>
+      </c>
+      <c r="AL33" s="3">
         <v>53820</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AM33" s="3">
         <v>1181081006688</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AN33" s="3">
         <v>53826.35</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AO33" s="3">
         <v>0.01</v>
       </c>
-      <c r="AJ33" s="2">
+      <c r="AP33" s="3">
+        <v>21944000</v>
+      </c>
+      <c r="AQ33" s="2">
         <v>46154</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AR33" s="3">
         <v>51015</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AS33" s="3">
         <v>388613323666</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AT33" s="3">
         <v>50980.25</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AU33" s="3">
         <v>0.04</v>
       </c>
-      <c r="AO33" s="2">
+      <c r="AV33" s="3">
+        <v>7618000</v>
+      </c>
+      <c r="AW33" s="2">
         <v>46154</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AX33" s="3">
         <v>104890</v>
       </c>
-      <c r="AQ33" s="3">
+      <c r="AY33" s="3">
         <v>2149844582606</v>
       </c>
-      <c r="AR33" s="3">
+      <c r="AZ33" s="3">
         <v>104212.94</v>
       </c>
-      <c r="AS33" s="3">
+      <c r="BA33" s="3">
         <v>0.05</v>
       </c>
-      <c r="AT33" s="2">
+      <c r="BB33" s="3">
+        <v>20497000</v>
+      </c>
+      <c r="BC33" s="2">
         <v>46154</v>
       </c>
-      <c r="AU33" s="3">
+      <c r="BD33" s="3">
         <v>50025</v>
       </c>
-      <c r="AV33" s="3">
+      <c r="BE33" s="3">
         <v>34417633800</v>
       </c>
-      <c r="AW33" s="3">
+      <c r="BF33" s="3">
         <v>49936.71</v>
       </c>
-      <c r="AX33" s="3">
+      <c r="BG33" s="3">
         <v>0.08</v>
       </c>
-      <c r="AY33" s="2">
+      <c r="BH33" s="3">
+        <v>688000</v>
+      </c>
+      <c r="BI33" s="2">
         <v>46154</v>
       </c>
-      <c r="AZ33" s="3">
+      <c r="BJ33" s="3">
         <v>114970</v>
       </c>
-      <c r="BA33" s="3">
+      <c r="BK33" s="3">
         <v>607406035217</v>
       </c>
-      <c r="BB33" s="3">
+      <c r="BL33" s="3">
         <v>114805.13</v>
       </c>
-      <c r="BC33" s="3">
+      <c r="BM33" s="3">
         <v>0.01</v>
+      </c>
+      <c r="BN33" s="3">
+        <v>5279000</v>
       </c>
     </row>
   </sheetData>
